--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -511,34 +511,46 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Urea</t>
+          <t>Water, Glycerin, Urea, Cetearyl Alcohol, Hydrogenated Cocoglycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Glyceryl Stearate SE, Ceramide NP, Lactic Acid, Arginine HCI, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Dimethicone, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Cetearyl Sulfate, Sodium Chloride</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Dimethicone [2,6] / Pentylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Hydrogenated Cocoglycerides, Butyrospermum Parkii (Shea) Butter, Ceramide NP, Arginine HCI, Carnitine, Carrageenan, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Decylene Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>4 flagged ingredient(s) in the full retailer INCI list (Dimethicone, Pentylene Glycol, Phenoxyethanol). 10 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 3 other product(s): Advanced Repair Lotion; Advanced Repair Hand Cream; Advanced Repair Cream, 8 OZ.</t>
+          <t>Source: Target, https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854. Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -565,29 +577,41 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Urea</t>
+          <t>Water, Glycerin, Cetearyl Alcohol, Glyceryl Glucosdie, Cyclomethicone, Soidum Lactate, Butyrospemum Parkii (Shea) Butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Glyceryl Stearate SE, Hydrogenated Coco-Glycerides, Arginine HCL, Sodium PCA, Dimethiconol, Lactic Acid, Chondrus Crispus (Carrageenan), Carnitine, Ceramide 3, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL, Sodium Chloride, Sodium Cetearyl Sulfate, 1,2-Hexanediol, Phenoxyethanol</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Cyclomethicone [1,2,6] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Glyceryl Glucosdie, Soidum Lactate, Butyrospemum Parkii (Shea) Butter, Methylpropanediol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Arginine HCL, Dimethiconol, Chondrus Crispus (Carrageenan), Carnitine, Ceramide 3, Mannitol, Sucrose, Citrulline, Glycogen, Histidine HCL, Glutamic Acid, Lysine HCL</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>4 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Cyclomethicone, Sodium Cetearyl Sulfate, 1,2-Hexanediol). 19 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 3 other product(s): Advanced Repair Cream, 16 OZ; Advanced Repair Hand Cream; Advanced Repair Cream, 8 OZ.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970. CONFLICT: Walmart printed list (Eucerin Advanced Repair Lotion, Fragrance Free, 16.9 fl oz) does not include Urea and its first ingredients differ from the brand-site text (Water, Glycerin, Urea). Both texts kept; not resolved. Walmart spellings kept as printed. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -619,29 +643,41 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Urea</t>
+          <t>Glycerin, Urea, Glyceryl Stearate, Dibutyl Adipate, Stearyl Alcohol, Dicaprylyl Ether, Cetearyl Alcohol, Sodium Lactate, Tapioca Starch, Glyceryl Stearate SE, Ceramide 3, Lactic Acid, Sodium PCA, Arginine HCL, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus Seed Extract, Dimethicone, Xanthan Gum, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Sodium Cetearyl Sulfate</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Dimethicone [2,6] / Pentylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dibutyl Adipate, Dicaprylyl Ether, Tapioca Starch, Ceramide 3, Arginine HCL, Carnitine, Helianthus Annuus Seed Extract, Decylene Glycol</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>4 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Dimethicone, Pentylene Glycol, Phenoxyethanol). 8 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 3 other product(s): Advanced Repair Cream, 16 OZ; Advanced Repair Lotion; Advanced Repair Cream, 8 OZ.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Advanced-Repair-Hand-Cream-Fragrance-Free-2-7-oz-Tube/11997314. CONFLICT: Walmart printed list (Eucerin Advanced Repair Hand Cream, Fragrance Free, 2.7 oz tube) starts Glycerin, Urea and has no Water, while the brand site prints Water, Glycerin, Urea. Both kept; not resolved. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -673,7 +709,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Water, Sodium Cocoamphoacetate, Sodium Myreth Sulfate</t>
+          <t>Water, Sodium Cocoamphoacetate, Sodium Myreth Sulfate, Lauryl Glucoside, Sodium Chloride, Citric Acid, Coco-Glucoside, Glycol Distearate, Glycerin, PEG-40 Hydrogenated Castor Oil, Polyquaternium-10, PEG-200 Hydrogenated Glyceryl Palmate, Diammonium Citrate, Sodium Acetate, Sodium Benzoate, Sodium Salicylate</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -682,33 +718,33 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate)</t>
+          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / Glycol Distearate [4] / PEG-40 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-) / PEG-200 Hydrogenated Glyceryl Palmate [1,2,4,5] (inferred: PEG-)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sodium Cocoamphoacetate</t>
+          <t>Sodium Cocoamphoacetate, Lauryl Glucoside, Polyquaternium-10, Diammonium Citrate, Sodium Acetate, Sodium Salicylate</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate); tier applies to printed subset only. 1 unknown ingredient(s) not in reference.</t>
+          <t>4 flagged ingredient(s) in the full retailer INCI list (Sodium Myreth Sulfate, Glycol Distearate, PEG-40 Hydrogenated Castor Oil). 6 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311. Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (Mild). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -735,34 +771,46 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Urea</t>
+          <t>Water, Glycerin, Urea, Cetearyl Alcohol, Hydrogenated Coco-Glycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Glyceryl Stearate SE, Ceramide NP, Lactic Acid, Arginine HCl, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Dimethicone, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Cetearyl Sulfate, Sodium Chloride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Dimethicone [2,6] / Pentylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Hydrogenated Coco-Glycerides, Butyrospermum Parkii (Shea) Butter, Ceramide NP, Arginine HCl, Carnitine, Carrageenan, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Decylene Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>4 flagged ingredient(s) in the full retailer INCI list (Dimethicone, Pentylene Glycol, Phenoxyethanol). 10 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 3 other product(s): Advanced Repair Cream, 16 OZ; Advanced Repair Lotion; Advanced Repair Hand Cream.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046. Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -802,7 +850,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat)</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -810,12 +858,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat.); tier applies to printed subset only.</t>
+          <t>1 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Alcohol Denat).</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 2 other product(s): Dark Spot Corrector Body Lotion; Night Cream.</t>
+          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. no retailer INCI found. Walmart and Amazon have no Dark Spot Corrector Body Cream listing (only the body lotion). Target search returned no results in this session; Ulta returned a holding page; CVS, Walgreens, Sephora, Dermstore not yet checked. Tier without the PFAS rule: Use Caution. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -847,7 +895,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Water, Alcohol Denat., Butylene Glycol</t>
+          <t>Water, Alcohol Denat., Butylene Glycol, Glycerin, Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Cetearyl Alcohol, Distarch Phosphate, Sodium Hyaluronate, Tocopherol, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dimethicone, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Xanthan Gum, Gellan Gum, Sodium Chloride, Phenoxyethanol, Ethylhexylglycerin, Trisodium EDTA, Citric Acid, Fragrance.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -856,33 +904,37 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Butylene Glycol [1,2]</t>
+          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Butylene Glycol [1,2] / Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Fragrance [1,2,4,8]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (Alcohol Denat., Butylene Glycol); tier applies to printed subset only.</t>
+          <t>6 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Butylene Glycol, Dimethicone). 14 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Moisture Boost Serum.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648. Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -909,34 +961,46 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Caprylic/Capric Triglyceride</t>
+          <t>Water, Glycerin, Caprylic/Capric Triglyceride, Alcohol Denat., Cocoglycerides, Cetearyl Alcohol, Isopropyl Palmitate, Cetyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Lauroyl Lysine, SodiumHyaluronate, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Synthetic Fluorphlogopite, SodiumStearoyl Glutamate, Citric Acid, Xanthan Gum, Phenoxyethanol, Ethylhexylglycerin, SodiumHydroxide, Trisodium EDTA, Titanium Dioxide, Tin Oxide, Iron Oxides.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Synthetic Fluorphlogopite [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Iron Oxides [1,2,3]</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Cocoglycerides, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Trisodium EDTA, Tin Oxide</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>5 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Synthetic Fluorphlogopite, Phenoxyethanol). 9 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130. Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Titanium Dioxide (CI 77891) not flagged: rubric conditional, not a concern in cream-based skincare. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -963,38 +1027,46 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Alcohol Denat.</t>
+          <t>Water, Glycerin, Alcohol Denat., Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Ceteary Alcohol, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Isobutylamido Thiazolyl Resorcinol, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Xanthan Gum, Sodium Stearoyl Glutamate, Ethylhexylglycerin, Phenoxyethanol, Trisodium EDTA, Citric Acid, Fragrance</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat)</t>
+          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Ceteary Alcohol, Dibutyl Adipate, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Trisodium EDTA</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat.); tier applies to printed subset only.</t>
+          <t>4 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Ethylhexylglycerin, Phenoxyethanol). 10 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 2 other product(s): Dark Spot Corrector Body Cream; Night Cream.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080. Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1021,38 +1093,46 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Avobenzone (3%), Homosalate (8%), Octisalate (4.5%), Octocrylene (9%)</t>
+          <t>Active: Avobenzone 3% , Homosalate 8%, Octisalate 4.5%, Octocrylene 9%. Inactive: Water, Glycerin, Alcohol Denat., Glyceryl Stearate, Silica, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Cetearyl Alcohol, Dibutyl Adipate, Silica Dimethyl Silylate, Tocopherol, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Xanthan Gum, Phenoxyethanol, Ethylhexylglycerin, Disodium EDTA, Sodium Chloride, Fragrance.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (8%) [2] / Octisalate (4.5%) [2] / Octocrylene (9%) [2]</t>
+          <t>Avobenzone (3%) [2] / Homosalate (8%) [2] / Octisalate (4.5%) [2] / Alcohol Denat. [4] (inferred: alcohol denat) / Silica [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Fragrance [1,2,4,8]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Octocrylene (9%)., Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Avobenzone (3%), Homosalate (8%), Octisalate (4.5%)); tier applies to printed subset only.</t>
+          <t>8 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (8%), Octisalate (4.5%)). 11 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095. Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1079,38 +1159,46 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Alcohol Denat.</t>
+          <t>Water, Glycerin, Alcohol Denat., Butyrospermum Parkii (Shea) Butter, Squalane, Cetearyl Isononanoate, Panthenol, Isopropyl Palmitate, Glyceryl Stearate Citrate, Cetearyl Alcohol, Hydrogenated Coco-Glycerides, Methylpropanediol, Lauroyl Lysine, Tocopherol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate, Xanthan Gum, Phenoxyethanol, Trisodium Ethylenediamine Disuccinate, Citric Acid, Fragrance.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat)</t>
+          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Butyrospermum Parkii (Shea) Butter, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat.); tier applies to printed subset only.</t>
+          <t>3 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Phenoxyethanol, Fragrance). 10 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 2 other product(s): Dark Spot Corrector Body Cream; Dark Spot Corrector Body Lotion.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313. Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1225,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Water, Alcohol Denat., Sodium Cocoamphoacetate</t>
+          <t>Water, Alcohol Denat., Sodium Cocoamphoacetate, Glycerin, Coco-Betaine, Lactic Acid, SodiumChloride, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside, Sodium Hydroxide, SodiumBenzoate.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1156,23 +1244,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sodium Cocoamphoacetate</t>
+          <t>Sodium Cocoamphoacetate, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat.); tier applies to printed subset only. 1 unknown ingredient(s) not in reference.</t>
+          <t>1 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat.). 4 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363. Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Use Caution. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1199,38 +1287,46 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Water, Alcohol Denat., Glycerin</t>
+          <t>Water, Alcohol Denat., Glycerin, Panthenol, Distarch Phosphate, Sodium Hyaluronate, Cetearyl Isononanoate, Isopropyl Palmitate, Lauroyl Lysine, Squalene, Tocopherol, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Cetyl Alcohol, Dehydroxanthan Gum, Xanthan Gum, Behenyl Alcohol, Citric Acid, Lactic Acid, Phenoxyethanol, Fragrance</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat)</t>
+          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Distarch Phosphate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat.); tier applies to printed subset only.</t>
+          <t>3 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Phenoxyethanol, Fragrance). 7 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional.</t>
+          <t>Source: Amazon, https://www.amazon.com/dp/B0CHD4M1FT. Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1353,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Water, Alcohol Denat., Butylene Glycol</t>
+          <t>Water, Alcohol Denat., Butylene Glycol, Glycerin, Sodium Hyaluronate, PEG-40 Hydrogenated Castor Oil, Sodium Ascorbyl Phosphate, Caprylyl Glycol, Citric Acid, Fragrance</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1266,15 +1362,19 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Butylene Glycol [1,2]</t>
+          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Butylene Glycol [1,2] / PEG-40 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-) / Fragrance [1,2,4,8]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sodium Ascorbyl Phosphate</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -1282,17 +1382,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (Alcohol Denat., Butylene Glycol); tier applies to printed subset only.</t>
+          <t>4 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Butylene Glycol, PEG-40 Hydrogenated Castor Oil). 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Dual Serum.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616. Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1419,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Coco-Betaine</t>
+          <t>Water, Glycerin, Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hyaluronate, Trisodium EDTA, Sodium Chloride, Sodium Benzoate</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1332,21 +1432,25 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>No flagged ingredients in the full retailer INCI list. 3 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479. Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1477,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hyaluronic acid, Gluco-Glycerol, APG Complex</t>
+          <t>Water, Glycerin, Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hyaluronate, Trisodium EDTA, Sodium Chloride, Sodium Benzoate</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1388,23 +1492,23 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Gluco-Glycerol, APG Complex</t>
+          <t>Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 2 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the full retailer INCI list. 3 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: Amazon, https://www.amazon.com/dp/B094NWLKKZ. Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1535,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Water, Mineral Oil, Octyldodecanol</t>
+          <t>Water, Mineral Oil, Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Glycerin, PEG-7 Hydrogenated Castor Oil, Benzyl Alcohol, Dimethicone, Methoxy PEG-22/Dodecyl Glycol Copolymer, PEG-45/Dodecyl Glycol Copolymer, Magnesium Sulfate, Lactic Acid, Ozokerite, PEG-2 Hydrogenated Castor Oil, Sorbitan Isostearate, Hydrogenated Castor Oil.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1440,28 +1544,32 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Mineral Oil [1]</t>
+          <t>Mineral Oil [1] / PEG-7 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-) / Dimethicone [2,6] / PEG-45/Dodecyl Glycol Copolymer [1,2,4,5] (inferred: PEG-) / PEG-2 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Methoxy PEG-22/Dodecyl Glycol Copolymer, Sorbitan Isostearate</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Mineral Oil); tier applies to printed subset only.</t>
+          <t>5 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Mineral Oil, PEG-7 Hydrogenated Castor Oil, Dimethicone). 2 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395. Walmart listing Eucerin Intensive Repair Body Lotion, Fragrance Free, 16.9 fl oz pump. First 3 match brand-site text. Brand listing prints no size, so the size match is not confirmed; status left at needs review. A 5 oz Very Dry Skin lotion on Walmart (22301266) has a different list (PEG-7 Hydrogenated Castor Oil in place of Octyldodecanol) and was not used. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1514,12 +1622,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. variant mismatch, not used: brand prints only Q10 as key ingredient. Walmart candidate 233160412 is Eucerin Q10 Anti-Wrinkle Night Cream with Pro-Retinol (contains Retinyl Palmitate, a different formula). Not clearly the same product. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1572,12 +1680,12 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 2 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 2 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. Candidate only, not confirmed. Walmart listing Eucerin Q10 Anti-Wrinkle Face Cream, 1.7 oz, Non-Comedogenic contains Ubiquinone and Shea Butter (the brand key ingredients), but the brand text is key-ingredient only, so the first-ingredient cross-check cannot be done. Another Walmart listing (633889049) reads Refer to product label. Candidate retailer list not used for grading: Walmart https://www.walmart.com/ip/Eucerin-Q10-Anti-Wrinkle-Face-Cream-for-Sensitive-Skin-1-7-Oz-Jar/25868522. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1630,12 +1738,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 2 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 2 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. CONFLICT, not used: Walmart listing Eucerin After Sun Moisturizing Lotion (6.7 fl oz) lists Glycyrrhetinic Acid but no Licochalcone A, which the brand lists. Its first ingredients (Water, Alcohol Denat.) also differ from the brand key list. Not confirmed. Candidate retailer list not used for grading: Walmart https://www.walmart.com/ip/Eucerin-Advanced-Hydration-After-Sun-Lotion-6-8-fl-oz-Tube/1041972542. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1667,34 +1775,46 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zinc Oxide (24%)</t>
+          <t>Active Ingredients: Zinc Oxide 24%... Inactive Ingredients: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Butyloctyl Salicylate, Ethylhexyl Pelargonate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol, Cyclopentasiloxane, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Dimethicone, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Beeswax, Hydroxyacetophenone, Sodium Chloride, PEG-12 Dimethicone Crosspolymer, 1,2-Hexanediol, Caprylyl Glycol, Tocopherol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Butyloctyl Salicylate [2] / Cetyl PEG/PPG-10/1 Dimethicone [2,6] (inferred: silicone) / Propylene Glycol [1,2] / Cyclopentasiloxane [1,2,6] / Dimethicone [2,6] / PEG-12 Dimethicone Crosspolymer [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2]</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>7 flagged ingredient(s) in the full retailer INCI list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol). 7 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 2 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion; Tinted Sensitive Mineral SPF 35 Face Sunscreen. Zinc Oxide treated as zinc oxide (non-nano) per addendum 2026-10-09; LOW TOX in lotions.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650. Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1721,38 +1841,46 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avobenzone (3%), Homosalate (10%), Octisalate (5%), Octocrylene (10%)</t>
+          <t>Active ingredients: Avobenzone 3%, Homosalate 10%, Octisalate 5%, Octocrylene 10%. Purpose: Sunscreen Inactive Ingredients: l-6 Stearate, Glycerin, Silica, Diethylhexyl Syringylidenemalonate, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Tocopherol (Vitamin E), Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Cetearyl Alcohol, Glyceryl Stearate, Phenoxyethanol, Polyglyceryl-6 Behenate, Disodium EDTA, Sodium Hyaluronate, Xanthan Gum, Potassium Hydroxide</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Octocrylene (10%) [2]</t>
+          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Silica [1,2] / Diethylhexyl Syringylidenemalonate [2] / Phenoxyethanol [1,2,4,5,8] / Potassium Hydroxide [4]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Octocrylene (10%)., l-6 Stearate, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Polyglyceryl-6 Behenate, Disodium EDTA</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)); tier applies to printed subset only.</t>
+          <t>7 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)). 12 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 3 other product(s): Clear Skin SPF 50 Face Sunscreen; Age Defense SPF 50 Face Sunscreen; Tinted Age Defense SPF 50 Face Sunscreen.</t>
+          <t>Source: Amazon, https://www.amazon.com/dp/B0DJTXV6XQ. Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1779,38 +1907,46 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avobenzone (3%), Homosalate (9%), Octisalate (4.5%), Octocrylene (9%)</t>
+          <t>Active Ingredients: Avobenzone 3%, Homosalate 9%, Octisalate 4.5%, Octocrylene 9%... Inactive Ingredients: Water, Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Styrene/Acrylates Copolymer, Butylene Glycol, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Tocopherol, Hydroxyacetophenone, Diethylhexyl Syringylidenemalonate, VP/Eicosene Copolymer, 1,2-Hexandiol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Potassium Hydroxide, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (9%) [2] / Octisalate (4.5%) [2] / Octocrylene (9%) [2]</t>
+          <t>Avobenzone (3%) [2] / Homosalate (9%) [2] / Octisalate (4.5%) [2] / Octocrylene (9%) [2] / Styrene/Acrylates Copolymer [1,4,6] / Butylene Glycol [1,2] / Diethylhexyl Syringylidenemalonate [2] / VP/Eicosene Copolymer [1,2,6] / Potassium Hydroxide [4]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, 1;2-Hexandiol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Avobenzone (3%), Homosalate (9%), Octisalate (4.5%)); tier applies to printed subset only.</t>
+          <t>9 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (9%), Octisalate (4.5%)). 11 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Advanced Hydration SPF 50 Sunscreen.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769. Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1837,38 +1973,46 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Avobenzone (3%), Homosalate (9%), Octisalate (4.5%), Octocrylene (9%)</t>
+          <t>Active Ingredients: Avobenzone 3%, Homosalate 9%, Octisalate 4.5%, Octocrylene 9%... Inactive Ingredients: Water, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Styrene/Acrylates Copolymer, Butylene Glycol, Diethylhexyl Syringylidenemalonate, VP/Eicosene Copolymer, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Tocopherol, Aloe Barbadensis Leaf Juice, 1,2-Hexandiol, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Potassium Hydroxide, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (9%) [2] / Octisalate (4.5%) [2] / Octocrylene (9%) [2]</t>
+          <t>Avobenzone (3%) [2] / Homosalate (9%) [2] / Octisalate (4.5%) [2] / Octocrylene (9%) [2] / Styrene/Acrylates Copolymer [1,4,6] / Butylene Glycol [1,2] / Diethylhexyl Syringylidenemalonate [2] / VP/Eicosene Copolymer [1,2,6] / Potassium Hydroxide [4]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, 1;2-Hexandiol, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Avobenzone (3%), Homosalate (9%), Octisalate (4.5%)); tier applies to printed subset only.</t>
+          <t>9 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (9%), Octisalate (4.5%)). 10 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Advanced Hydration SPF 50 Sunscreen Spray.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962. Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1895,34 +2039,46 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zinc Oxide (24%)</t>
+          <t>Active Ingredients: Zinc Oxide 24%... Inactive Ingredients: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Butyloctyl Salicylate, Ethylhexyl Pelargonate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol, Cyclopentasiloxane, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Dimethicone, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Beeswax, Hydroxyacetophenone, Sodium Chloride, PEG-12 Dimethicone Crosspolymer, 1,2-Hexanediol, Caprylyl Glycol, Tocopherol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Butyloctyl Salicylate [2] / Cetyl PEG/PPG-10/1 Dimethicone [2,6] (inferred: silicone) / Propylene Glycol [1,2] / Cyclopentasiloxane [1,2,6] / Dimethicone [2,6] / PEG-12 Dimethicone Crosspolymer [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2]</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>7 flagged ingredient(s) in the full retailer INCI list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol). 7 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 2 other product(s): Sensitive Mineral SPF 50 Sunscreen; Tinted Sensitive Mineral SPF 35 Face Sunscreen. Zinc Oxide treated as zinc oxide (non-nano) per addendum 2026-10-09; LOW TOX in lotions.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849. Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1949,38 +2105,46 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avobenzone (3%), Homosalate (10%), Octisalate (5%), Octocrylene (10%)</t>
+          <t>Active: Avobenzone 3%, Homosalate 10%, Octisalate 5%, Octocrylene 10%... Inactive: Water, Alcohol Denat., Butyloctyl Salicylate, Silica, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Behenyl Alcohol, Butylene Glycol Dicaprylate/Dicaprate, Cetearyl Alcohol, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Tocopherol, Dimethicone, Silica Dimethyl Silylate, Diethylhexyl Syringylidenemalonate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Phenoxyethanol, Glycerin, Xanthan Gum, Ethylhexylglycerin, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Cetyl Alcohol, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Octocrylene (10%) [2]</t>
+          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Octocrylene (10%) [2] / Alcohol Denat. [4] (inferred: alcohol denat) / Butyloctyl Salicylate [2] / Silica [1,2] / Dimethicone [2,6] / Diethylhexyl Syringylidenemalonate [2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)); tier applies to printed subset only.</t>
+          <t>11 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)). 18 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 3 other product(s): Advanced Hydration Ultra-Light SPF 50 Face Sunscreen; Age Defense SPF 50 Face Sunscreen; Tinted Age Defense SPF 50 Face Sunscreen.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371. Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2007,38 +2171,46 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Avobenzone (3%), Homosalate (10%), Octisalate (5%), Octocrylene (10%)</t>
+          <t>Active Ingredients: Avobenzone 3%, Homosalate 10%, Octisalate 5%, Octocrylene 10%... Inactive Ingredients: Water, Alcohol Denat., Butyloctyl Salicylate, Silica, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Behenyl Alcohol, Butylene Glycol Dicaprylate/Dicaprate, Cetearyl Alcohol, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Tocopherol, Dimethicone, Silica Dimethyl Silylate, Diethylhexyl Syringylidenemalonate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Phenoxyethanol, Glycerin, Xanthan Gum, Ethylhexylglycerin, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Cetyl Alcohol, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Octocrylene (10%) [2]</t>
+          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Octocrylene (10%) [2] / Alcohol Denat. [4] (inferred: alcohol denat) / Butyloctyl Salicylate [2] / Silica [1,2] / Dimethicone [2,6] / Diethylhexyl Syringylidenemalonate [2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)); tier applies to printed subset only.</t>
+          <t>11 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)). 18 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 3 other product(s): Advanced Hydration Ultra-Light SPF 50 Face Sunscreen; Clear Skin SPF 50 Face Sunscreen; Tinted Age Defense SPF 50 Face Sunscreen.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848. Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2065,34 +2237,46 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zinc Oxide (24%)</t>
+          <t>Active: Zinc Oxide 24% Inactive: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Butyloctyl Salicylate, Ethylhexyl Pelargonate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol, Cyclopentasiloxane, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Dimethicone, Diethylhexyl Syringylidenemalonate, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Tocopherol (Vitamin E), Triethoxycaprylylsilane, Beeswax, Hydroxyacetophenone, Sodium Chloride, PEG-12 Dimethicone Crosspolymer, 1,2-Hexanediol, Caprylyl Glycol, Jojoba Esters, Silica, Polyglyceryl-6 Polyricinoleate, Iron Oxides</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Butyloctyl Salicylate [2] / Cetyl PEG/PPG-10/1 Dimethicone [2,6] (inferred: silicone) / Propylene Glycol [1,2] / Cyclopentasiloxane [1,2,6] / Dimethicone [2,6] / Diethylhexyl Syringylidenemalonate [2] / PEG-12 Dimethicone Crosspolymer [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Silica [1,2] / Iron Oxides [1,2,3]</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>10 flagged ingredient(s) in the full retailer INCI list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol). 13 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 2 other product(s): Sensitive Mineral SPF 50 Sunscreen; Baby Sensitive Mineral SPF 50 Sunscreen Lotion. Zinc Oxide treated as zinc oxide (non-nano) per addendum 2026-10-09; LOW TOX in lotions.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195. Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2119,38 +2303,46 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avobenzone (3%), Homosalate (10%), Octisalate (5%), Octocrylene (10%)</t>
+          <t>Active ingredients: Avobenzone 3%, Homosalate 10%, Octisalate 5%, Octocrylene 10% Inactive ingredients: Water, Alcohol Denat., Butyloctyl Salicylate, Silica, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Behenyl Alcohol, Butylene Glycol Dicaprylate/Dicaprate, Cetearyl Alcohol, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Hyaluronate, L-Carnitine, Sodium Ascorbyl Phosphate, Tocopherol (Vitamin E), Hydroxyacetophenone, Diethylhexyl Syringylidenemalonate, Dimethicone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Glycerin, Phenoxyethanol, Xanthan Gum, Ethylhexylglycerin, Polyglyceryl-6 Behenate, Cetyl Alcohol, Cellulose Gum, 1,2-Hexanediol, Caprylyl Glycol, Sodium Polyacrylate, Disodium EDTA, Iron Oxides</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Octocrylene (10%) [2]</t>
+          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Octocrylene (10%) [2] / Alcohol Denat. [4] (inferred: alcohol denat) / Butyloctyl Salicylate [2] / Silica [1,2] / Diethylhexyl Syringylidenemalonate [2] / Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / 1,2-Hexanediol [1,2] / Iron Oxides [1,2,3]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Polyglyceryl-6 Behenate, Disodium EDTA</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)); tier applies to printed subset only.</t>
+          <t>13 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)). 18 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 3 other product(s): Advanced Hydration Ultra-Light SPF 50 Face Sunscreen; Clear Skin SPF 50 Face Sunscreen; Age Defense SPF 50 Face Sunscreen.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307. Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2390,12 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Avobenzone (3%), Homosalate (7%), Octisalate (4.5%)); tier applies to printed subset only.</t>
+          <t>4 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Avobenzone (3%), Homosalate (7%), Octisalate (4.5%)).</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional.</t>
+          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. no retailer INCI found. No Eucerin Advanced Hydration SPF 30 spray listing on Walmart or Amazon (searched). Dermstore and CVS not yet checked. Tier without the PFAS rule: Avoid (Mild). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2235,34 +2427,46 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Water, Urea, Glycerin</t>
+          <t>Water, Urea, Glycerin, Cetearyl Alcohol, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Sodium Lactate, Glyceryl Stearate SE, Distarch Phosphate, Ceramide NP, Lactic Acid, Sodium PCA, Arginine HCl, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Sorbitan Stearate, Dimethicone, Phenoxyethanol, Carbomer, Sodium Cetearyl Sulfate, Sodium Chloride</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Distarch Phosphate, Ceramide NP, Arginine HCl, Carnitine, Helianthus Annuus (Sunflower) Seed Oil</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>4 flagged ingredient(s) in the full retailer INCI list (Dimethicone, Phenoxyethanol, Carbomer). 7 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Roughness Relief Lotion.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082. Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2289,34 +2493,46 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Water, Urea, Glycerin</t>
+          <t>Water, Urea, Glycerin, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Cetearyl Alcohol, Arginine HCL, Sodium PCA, Lactic Acid, Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Ceramide NP, Alanine, Threonine, Glutamic Acid, Lysine HCL, Sodium Chloride, 1,2-Hexanediol, Phenoxyethanol, Potassium Sorbate.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Arginine HCL, Carnitine, Mannitol, Sucrose, Citrulline, Glycogen, Histidine HCL, Ceramide NP, Glutamic Acid, Lysine HCL</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>2 flagged ingredient(s) in the full retailer INCI list (1,2-Hexanediol, Phenoxyethanol). 16 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Roughness Relief Cream.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111. Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2343,38 +2559,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (2%)</t>
+          <t>Active Ingredient: 2% colloidal oatmeal - Inactive Ingredients: Water, Isopropyl Palmitate, Glycerin, Cetearyl Alcohol, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Sodium Myreth Sulfate, Cetearyl Isononanoate, Xanthan Gum, Ceramide NP, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Citric Acid, Sodium Chloride, Phenoxyethanol, Carbomer, Sodium Hydroxide, Pentylene Glycol, Decylene Glycol, Sodium Benzoate</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (Mild)</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Pentylene Glycol [1,2]</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (2%)</t>
+          <t>colloidal oatmeal (2%)-, Sodium Cocoamphoacetate, C12-15 Alkyl Benzoate, Ceramide NP, Arginine HCl, Carnitine, Lauryl Glucoside, Decylene Glycol</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>4 flagged ingredient(s) in the full retailer INCI list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer). 8 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851. Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (Mild). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2401,38 +2621,46 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (1%)</t>
+          <t>Active Ingredient: Colloidal Oatmeal 1% Inactive Ingredients: Water, Glycerin, Ricinus Communis (Castor) Seed Oil, Mineral Oil, Cetyl Alcohol, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Cetyl Palmitate, PEG-40 Stearate, Glycyrrhiza Inflata Root Extract, Ceramide NP, 1,2-Hexanediol, Phenoxyethanol, Piroctone Olamine, Caprylyl Glycol, Ethylhexylglycerin, Benzyl Alcohol, Citric Acid.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Mineral Oil [1] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (1%)</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Colloidal Oatmeal (1%), Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Piroctone Olamine</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol). 5 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 2 other product(s): Eczema Relief Flare-Up Treatment; Baby Eczema Relief Cream. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571. Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2459,38 +2687,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal, Water, Glycerin</t>
+          <t>Active ingredient: Colloidal Oatmeal 1% ...... Skin Protectant. Inactive Ingredients: Water, Glycerin, Alcohol Denat., Octyldodecanol, Caprylic/Capric Triglyceride, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Ceramide NP, Phytosphingosine, Oleic Acid, Behenyl Alcohol, Cetyl Alcohol, Gellan Gum, Xanthan Gum, Hydroxyacetophenone, Caprylyl Glycol, Citric Acid.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Alcohol Denat. [4] (inferred: alcohol denat)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal</t>
+          <t>Colloidal Oatmeal (1%), Glycyrrhiza Inflata Root Extract, Ceramide NP, Gellan Gum, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>1 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat.). 5 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Eucerin Baby Eczema Relief Hydrogel. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083. Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Use Caution. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2517,38 +2749,46 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (1%)</t>
+          <t>Colloidal Oatmeal 1% Inactive Ingredients: Water, Glycerin, Mineral Oil, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Cetyl Alcohol, Glyceryl Stearate, Cetyl Palmitate, PEG-40 Stearate, Glycyrrhiza Inflata Root Extract, Ceramide NP, Decylene Glycol, 1,2-Hexanediol, Phenoxyethanol, Piroctone Olamine, Caprylyl Glycol, Ethylhexylglycerin, Citric Acid, Menthoxypropanediol, Trisodium EDTA, Benzyl Alcohol, BHT.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Mineral Oil [1] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (1%)</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>Colloidal Oatmeal (1%), Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Decylene Glycol, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA, BHT</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol). 9 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 2 other product(s): Eczema Relief Cream; Baby Eczema Relief Cream. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674. Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2575,38 +2815,46 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Menthol (0.1%)</t>
+          <t>Active Ingredients: Menthol 0.1% (external analgesic / anti-itch)...Inactive Ingredients: Water, Glycerin, Alcohol Denat., Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Triisostearin, Stearyl Alcohol, Laureth-9, Palmitic Acid, Stearic Acid, Distarch Phosphate, Dimethicone, Glyceryl Stearate, Cetyl Alcohol, PEG-100 Stearate, Sorbitan Stearate, Arginine HCl, Tocopherol, Ceramide NP, Sodium Citrate, Citric Acid, Myristic Acid, Arachidic Acid, Oleic Acid, Benzyl Alcohol, Pentylene Glycol, Ethylhexylglycerin, 4-t-butylcyclohexanol, Menthoxypropanediol, Carbomer, Sodium Hydroxide, Trisodium EDTA.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Laureth-9 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Pentylene Glycol [1,2] / Ethylhexylglycerin [4,5] / Carbomer [1,4,6]</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Menthol (0.1%)</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Menthol (0.1%), Hydrogenated Coco-Glycerides, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Arginine HCl, Ceramide NP, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Trisodium EDTA</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>7 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Laureth-9, Dimethicone). 13 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664. Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2633,34 +2881,46 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Cetyl Palmitate</t>
+          <t>Water, Glycerin, Cetyl Palmitate, Mineral Oil, Caprylic-Capric-Triglyceride, Octyldodecanol, Cetyl Alcohol, Glyceryl Stearate, Colloidal Oatmeal (Skin Protectant), Dimethicone, Methylpropanediol, PEG-40 Stearate, Phenoxyethanol, 1-2-Hexanediol, Polyglyceryl-2 Caprate, Piroctone Olamine, Benzyl Alcohol, Carbomer, Decylene Glycol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Mineral Oil [1] / Dimethicone [2,6] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6]</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Caprylic-Capric-Triglyceride, Colloidal Oatmeal, Methylpropanediol, 1-2-Hexanediol, Polyglyceryl-2 Caprate, Piroctone Olamine, Decylene Glycol</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>5 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, Dimethicone, PEG-40 Stearate). 7 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Skin Calming Cream.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149. Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2687,34 +2947,46 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Cetyl Palmitate</t>
+          <t>Water, Glycerin, Cetyl Palmitate, Mineral Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Cetyl Alcohol, Glyceryl Stearate, Colloidal Oatmeal, Dimethicone, Methylpropanediol, PEG-40 Stearate, 1,2-Hexanediol, Phenoxyethanol, Piroctone Olamine, Carbomer, Benzyl Alcohol, Polyglyceryl-2 Caprate, Decylene Glycol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Mineral Oil [1] / Dimethicone [2,6] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6]</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate, Decylene Glycol</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference.</t>
+          <t>6 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, Dimethicone, PEG-40 Stearate). 5 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Skin Calming Lotion.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299. Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2762,12 +3034,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Octisalate (3.5)); tier applies to printed subset only.</t>
+          <t>1 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Octisalate (3.5)).</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional.</t>
+          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. no retailer INCI found. Walmart listing 912642578 prints no ingredient text; Amazon listings B082D8S4W3 and B00KIHJO3E print no ingredient text. Target not available in this session. Dermstore and CVS not yet checked. Tier without the PFAS rule: Use Caution. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2820,12 +3092,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. Candidate only, not used. Amazon listing is Eucerin Daily Hydration Lotion, Multipack, 3 x 16.9 fl oz. Its list contains Helianthus Annuus Seed Oil, matching the brand key ingredient (Sunflower Seed oil), but the multipack variant is not a clear match for the brand single product, and the brand prints no size. Candidate retailer list not used for grading: Amazon https://www.amazon.com/dp/B00AYSBR96. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2857,7 +3129,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Water, Petrolatum, Mineral Oil</t>
+          <t>Water, Petrolatum, Mineral Oil, Ceresin, Lanolin Alcohol, Phenoxyethanol, Piroctone Olamine</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2866,15 +3138,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
+          <t>Petrolatum [1] / Mineral Oil [1] / Phenoxyethanol [1,2,4,5,8]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Piroctone Olamine</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -2882,17 +3158,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil); tier applies to printed subset only.</t>
+          <t>3 flagged ingredient(s) in the full retailer INCI list (Petrolatum, Mineral Oil, Phenoxyethanol). 3 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749. Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2919,7 +3195,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mineral Oil, Isopropyl Palmitate, Sorbitol</t>
+          <t>Water, Mineral Oil, Isopropyl Palmitate, Sorbitol, Propylene Glycol, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Cetyl Palmitate, Magnesium Sulfate, Aluminum Stearates, Phenoxyethanol, Lanolin Alcohol, Sodium Citrate, Citric Acid, Potassium Sorbate.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2928,33 +3204,37 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Mineral Oil [1]</t>
+          <t>Mineral Oil [1] / Propylene Glycol [1,2] / Aluminum Stearates [3] (inferred: aluminum) / Phenoxyethanol [1,2,4,5,8]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>carcinogen in leave-on</t>
+          <t>heavy metals, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Mineral Oil); tier applies to printed subset only.</t>
+          <t>4 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, Propylene Glycol, Aluminum Stearates). 3 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298. Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3282,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Eucerin Eczema Relief Hydrogel. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. Candidate only, not confirmed. Walmart Eucerin Baby Eczema Relief Hydrogel, 5 fl oz: its printed Ingredients field does not include Colloidal Oatmeal, the brand active, so the brand Colloidal Oatmeal, Water, Glycerin pattern cannot be confirmed. Water and Glycerin appear first. Candidate retailer list not used for grading: Walmart https://www.walmart.com/ip/Eucerin-Baby-Eczema-Hydrogel-5oz-Tube/13173618198. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3039,38 +3319,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (2%)</t>
+          <t>Active Ingredient: 2% colloidal oatmeal - Inactive Ingredients: Water, Isopropyl Palmitate, Glycerin, Cetearyl Alcohol, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Sodium Myreth Sulfate, Cetearyl Isononanoate, Xanthan Gum, Ceramide NP, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Citric Acid, Sodium Chloride, Phenoxyethanol, Carbomer, Sodium Hydroxide, Pentylene Glycol, Decylene Glycol, Sodium Benzoate</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (Mild)</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Pentylene Glycol [1,2]</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (2%)</t>
+          <t>colloidal oatmeal (2%)-, Sodium Cocoamphoacetate, C12-15 Alkyl Benzoate, Ceramide NP, Arginine HCl, Carnitine, Lauryl Glucoside, Decylene Glycol</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>4 flagged ingredient(s) in the full retailer INCI list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer). 8 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271. Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (Mild). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3402,12 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate); tier applies to printed subset only.</t>
+          <t>1 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Sodium Myreth Sulfate).</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional.</t>
+          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. no retailer INCI found. Walmart 682440208 and 14819669289 print no ingredient text; Amazon B01G7L6YDW shows only shea butter and B0C4WG48N9 shows no list. Target not available in this session. Tier without the PFAS rule: Avoid (Mild). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3155,38 +3439,46 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (1%)</t>
+          <t>Active Ingredient: Colloidal Oatmeal 1% (Skin protectant). Inactive Ingredients: Water, Glycerin, Ricinus Communis (Castor) Seed Oil, Mineral Oil, Cetyl Alcohol, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Cetyl Palmitate, PEG-40 Stearate, Glycyrrhiza Inflata Root Extract, Ceramide NP, 1,2-Hexanediol, Phenoxyethanol, Piroctone Olamine, Caprylyl Glycol, Ethylhexylglycerin, Benzyl Alcohol, Citric Acid.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Mineral Oil [1] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (1%)</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>Colloidal Oatmeal (1%), Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Piroctone Olamine</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol). 5 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Identical printed text on 2 other product(s): Eczema Relief Cream; Eczema Relief Flare-Up Treatment. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944. Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3526,12 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed subset per reference. 1 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site publishes a partial list (key/active ingredients only, no full INCI); tier is provisional. Unknown ingredients left unscored; tier does not account for them.</t>
+          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. Candidate only, not confirmed. Walmart Eucerin Baby Lotion, 13.5 fl oz, Fragrance Free lists Panthenol, the INCI name for the brand key ingredient Dexpanthenol. Brand printed only one key ingredient, so the first-ingredient cross-check cannot be done. Size not printed on brand listing. Candidate retailer list not used for grading: Walmart https://www.walmart.com/ip/Eucerin-Baby-Lotion-Fragrance-Free-13-5-fl-oz-Bottle/50463431. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -520,17 +520,17 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Dimethicone [2,6] / Pentylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate)</t>
+          <t>Dimethicone [2,6] / Pentylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Decylene Glycol [1,2] (inferred: -glycol) / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Hydrogenated Cocoglycerides, Butyrospermum Parkii (Shea) Butter, Ceramide NP, Arginine HCI, Carnitine, Carrageenan, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Decylene Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+          <t>unknown — manual review needed: Hydrogenated Cocoglycerides, Butyrospermum Parkii (Shea) Butter, Ceramide NP, Carnitine, Carrageenan, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -540,12 +540,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the full retailer INCI list (Dimethicone, Pentylene Glycol, Phenoxyethanol). 10 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Source: Target, https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854. Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). Ingredient source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -596,7 +596,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Glyceryl Glucosdie, Soidum Lactate, Butyrospemum Parkii (Shea) Butter, Methylpropanediol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Arginine HCL, Dimethiconol, Chondrus Crispus (Carrageenan), Carnitine, Ceramide 3, Mannitol, Sucrose, Citrulline, Glycogen, Histidine HCL, Glutamic Acid, Lysine HCL</t>
+          <t>unknown — manual review needed: glyceryl glucoside, butyrospermum parkii (shea) butter, Methylpropanediol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Dimethiconol, Chondrus Crispus (Carrageenan), Carnitine, Ceramide 3, Mannitol, Sucrose, Citrulline, Glycogen, Glutamic Acid, Lysine HCL</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Cyclomethicone, Sodium Cetearyl Sulfate, 1,2-Hexanediol). 19 unknown ingredient(s) not in reference.</t>
+          <t>4 flagged ingredient(s) in the printed list (Cyclomethicone, Sodium Cetearyl Sulfate, 1,2-Hexanediol); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970. CONFLICT: Walmart printed list (Eucerin Advanced Repair Lotion, Fragrance Free, 16.9 fl oz) does not include Urea and its first ingredients differ from the brand-site text (Water, Glycerin, Urea). Both texts kept; not resolved. Walmart spellings kept as printed. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Glycerin, Urea, Glyceryl Stearate, Dibutyl Adipate, Stearyl Alcohol, Dicaprylyl Ether, Cetearyl Alcohol, Sodium Lactate, Tapioca Starch, Glyceryl Stearate SE, Ceramide 3, Lactic Acid, Sodium PCA, Arginine HCL, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus Seed Extract, Dimethicone, Xanthan Gum, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Sodium Cetearyl Sulfate</t>
+          <t>Active Ingredients: CERAMIDE 3, NATURAL MOISTURIZING FACTORS Inactive Ingredients: Water, Glycerin, Urea, Glyceryl Stearate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Stearyl Alcohol, Dicaprylyl Ether, Cetearyl Alcohol, Sodium Lactate, Tapioca Starch, Glyceryl Stearate SE, Ceramide NP, Lactic Acid, Sodium PCA, Arginine HCI, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Dimethicone, Xanthan Gum, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Sodium Cetearyl Sulfate, Sodium Chloride.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -652,17 +652,17 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Dimethicone [2,6] / Pentylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate)</t>
+          <t>Dimethicone [2,6] / Pentylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Decylene Glycol [1,2] (inferred: -glycol) / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Dibutyl Adipate, Dicaprylyl Ether, Tapioca Starch, Ceramide 3, Arginine HCL, Carnitine, Helianthus Annuus Seed Extract, Decylene Glycol</t>
+          <t>unknown — manual review needed: CERAMIDE 3, NATURAL MOISTURIZING FACTORS, Hydrogenated Coco-Glycerides, Butyl Adipate, Dicaprylyl Ether, Tapioca Starch, Ceramide NP, Carnitine, Helianthus Annuus (Sunflower) Seed Oil</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Dimethicone, Pentylene Glycol, Phenoxyethanol). 8 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Advanced-Repair-Hand-Cream-Fragrance-Free-2-7-oz-Tube/11997314. CONFLICT: Walmart printed list (Eucerin Advanced Repair Hand Cream, Fragrance Free, 2.7 oz tube) starts Glycerin, Urea and has no Water, while the brand site prints Water, Glycerin, Urea. Both kept; not resolved. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / Glycol Distearate [4] / PEG-40 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-) / PEG-200 Hydrogenated Glyceryl Palmate [1,2,4,5] (inferred: PEG-)</t>
+          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / Glycol Distearate [4] / PEG-40 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-) / Polyquaternium-10 [2] (inferred: -nium quat) / PEG-200 Hydrogenated Glyceryl Palmate [1,2,4,5] (inferred: PEG-)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sodium Cocoamphoacetate, Lauryl Glucoside, Polyquaternium-10, Diammonium Citrate, Sodium Acetate, Sodium Salicylate</t>
+          <t>unknown — manual review needed: Sodium Cocoamphoacetate, Lauryl Glucoside, Diammonium Citrate, Sodium Acetate, Sodium Salicylate</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the full retailer INCI list (Sodium Myreth Sulfate, Glycol Distearate, PEG-40 Hydrogenated Castor Oil). 6 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Glycol Distearate, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311. Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (Mild). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -780,17 +780,17 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Dimethicone [2,6] / Pentylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate)</t>
+          <t>Dimethicone [2,6] / Pentylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Decylene Glycol [1,2] (inferred: -glycol) / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hydrogenated Coco-Glycerides, Butyrospermum Parkii (Shea) Butter, Ceramide NP, Arginine HCl, Carnitine, Carrageenan, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Decylene Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+          <t>unknown — manual review needed: Hydrogenated Coco-Glycerides, Butyrospermum Parkii (Shea) Butter, Ceramide NP, Carnitine, Carrageenan, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the full retailer INCI list (Dimethicone, Pentylene Glycol, Phenoxyethanol). 10 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046. Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -837,38 +837,46 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Alcohol Denat.</t>
+          <t>Water, Glycerin, Alcohol Denat., Cetearyl Alcohol, Diisopropyl Adipate, Panthenol, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Behenyl Alcohol, Cetyl Palmitate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Sodium Hyaluronate, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Citric Acid, Tapioca Starch, Xanthan Gum, Pantolactone, Trisodium EDTA, Ethylhexylglycerin, Caprylyl Glycol, Phenoxyethanol, Fragrance</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat)</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Diisopropyl Adipate, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Tapioca Starch, Pantolactone, Trisodium EDTA</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Alcohol Denat).</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. no retailer INCI found. Walmart and Amazon have no Dark Spot Corrector Body Cream listing (only the body lotion). Target search returned no results in this session; Ulta returned a holding page; CVS, Walgreens, Sephora, Dermstore not yet checked. Tier without the PFAS rule: Use Caution. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -908,13 +916,13 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Butylene Glycol [1,2] / Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Fragrance [1,2,4,8]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Butylene Glycol [1,2] / Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -924,12 +932,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Butylene Glycol, Dimethicone). 14 unknown ingredient(s) not in reference.</t>
+          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, Dimethicone); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648. Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -974,13 +982,13 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Synthetic Fluorphlogopite [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Iron Oxides [1,2,3]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Synthetic Fluorphlogopite [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Iron Oxides [1,2,3]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Cocoglycerides, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Trisodium EDTA, Tin Oxide</t>
+          <t>unknown — manual review needed: Cocoglycerides, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Trisodium EDTA, Tin Oxide</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -990,12 +998,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Synthetic Fluorphlogopite, Phenoxyethanol). 9 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Synthetic Fluorphlogopite, Phenoxyethanol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130. Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Titanium Dioxide (CI 77891) not flagged: rubric conditional, not a concern in cream-based skincare. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1040,13 +1048,13 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Ceteary Alcohol, Dibutyl Adipate, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1056,12 +1064,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Ethylhexylglycerin, Phenoxyethanol). 10 unknown ingredient(s) not in reference.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080. Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. Ingredient source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1102,17 +1110,17 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (8%) [2] / Octisalate (4.5%) [2] / Alcohol Denat. [4] (inferred: alcohol denat) / Silica [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Fragrance [1,2,4,8]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Alcohol Denat [4] (inferred: alcohol denat) / Silica [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Octocrylene (9%)., Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA</t>
+          <t>unknown — manual review needed: Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1122,12 +1130,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (8%), Octisalate (4.5%)). 11 unknown ingredient(s) not in reference.</t>
+          <t>9 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095. Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1172,13 +1180,13 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Butyrospermum Parkii (Shea) Butter, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate</t>
+          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1188,12 +1196,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Phenoxyethanol, Fragrance). 10 unknown ingredient(s) not in reference.</t>
+          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313. Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1238,24 +1246,24 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat)</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sodium Cocoamphoacetate, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside</t>
+          <t>unknown — manual review needed: Sodium Cocoamphoacetate, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat.). 4 unknown ingredient(s) not in reference.</t>
+          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363. Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Use Caution. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1300,13 +1308,13 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Distarch Phosphate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum</t>
+          <t>unknown — manual review needed: Distarch Phosphate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1316,12 +1324,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Phenoxyethanol, Fragrance). 7 unknown ingredient(s) not in reference.</t>
+          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Source: Amazon, https://www.amazon.com/dp/B0CHD4M1FT. Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. Ingredient source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1366,13 +1374,13 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Butylene Glycol [1,2] / PEG-40 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-) / Fragrance [1,2,4,8]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Butylene Glycol [1,2] / PEG-40 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-) / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1382,12 +1390,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Butylene Glycol, PEG-40 Hydrogenated Castor Oil). 1 unknown ingredient(s) not in reference.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616. Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1434,18 +1442,18 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the full retailer INCI list. 3 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 3 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479. Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 6.8 FL OZ. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1492,18 +1500,18 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the full retailer INCI list. 3 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 3 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Source: Amazon, https://www.amazon.com/dp/B094NWLKKZ. Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 13.5 FL OZ. Ingredient source: Amazon (https://www.amazon.com/dp/B094NWLKKZ).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1554,7 +1562,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Methoxy PEG-22/Dodecyl Glycol Copolymer, Sorbitan Isostearate</t>
+          <t>unknown — manual review needed: Methoxy PEG-22/Dodecyl Glycol Copolymer, Sorbitan Isostearate</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1564,12 +1572,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Mineral Oil, PEG-7 Hydrogenated Castor Oil, Dimethicone). 2 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-7 Hydrogenated Castor Oil, Dimethicone); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395. Walmart listing Eucerin Intensive Repair Body Lotion, Fragrance Free, 16.9 fl oz pump. First 3 match brand-site text. Brand listing prints no size, so the size match is not confirmed; status left at needs review. A 5 oz Very Dry Skin lotion on Walmart (22301266) has a different list (PEG-7 Hydrogenated Castor Oil in place of Octyldodecanol) and was not used. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1616,18 +1624,18 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>unknown — manual review needed: Q10</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 1 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. variant mismatch, not used: brand prints only Q10 as key ingredient. Walmart candidate 233160412 is Eucerin Q10 Anti-Wrinkle Night Cream with Pro-Retinol (contains Retinyl Palmitate, a different formula). Not clearly the same product. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1674,18 +1682,18 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Q10, Shea Butter</t>
+          <t>unknown — manual review needed: Q10, Shea Butter</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 2 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 2 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. Candidate only, not confirmed. Walmart listing Eucerin Q10 Anti-Wrinkle Face Cream, 1.7 oz, Non-Comedogenic contains Ubiquinone and Shea Butter (the brand key ingredients), but the brand text is key-ingredient only, so the first-ingredient cross-check cannot be done. Another Walmart listing (633889049) reads Refer to product label. Candidate retailer list not used for grading: Walmart https://www.walmart.com/ip/Eucerin-Q10-Anti-Wrinkle-Face-Cream-for-Sensitive-Skin-1-7-Oz-Jar/25868522. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1732,18 +1740,18 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Glycyrrhetinic Acid, Licochalcone A</t>
+          <t>unknown — manual review needed: Glycyrrhetinic Acid, Licochalcone A</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 2 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 2 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. CONFLICT, not used: Walmart listing Eucerin After Sun Moisturizing Lotion (6.7 fl oz) lists Glycyrrhetinic Acid but no Licochalcone A, which the brand lists. Its first ingredients (Water, Alcohol Denat.) also differ from the brand key list. Not confirmed. Candidate retailer list not used for grading: Walmart https://www.walmart.com/ip/Eucerin-Advanced-Hydration-After-Sun-Lotion-6-8-fl-oz-Tube/1041972542. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1794,7 +1802,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1804,12 +1812,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the full retailer INCI list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol). 7 unknown ingredient(s) not in reference.</t>
+          <t>7 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650. Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1850,17 +1858,17 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Silica [1,2] / Diethylhexyl Syringylidenemalonate [2] / Phenoxyethanol [1,2,4,5,8] / Potassium Hydroxide [4]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Silica [1,2] / Diethylhexyl Syringylidenemalonate [2] / Phenoxyethanol [1,2,4,5,8] / Potassium Hydroxide [4]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Octocrylene (10%)., l-6 Stearate, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Polyglyceryl-6 Behenate, Disodium EDTA</t>
+          <t>unknown — manual review needed: l-6 Stearate, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Polyglyceryl-6 Behenate, Disodium EDTA</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1870,12 +1878,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)). 12 unknown ingredient(s) not in reference.</t>
+          <t>8 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Source: Amazon, https://www.amazon.com/dp/B0DJTXV6XQ. Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1916,17 +1924,17 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (9%) [2] / Octisalate (4.5%) [2] / Octocrylene (9%) [2] / Styrene/Acrylates Copolymer [1,4,6] / Butylene Glycol [1,2] / Diethylhexyl Syringylidenemalonate [2] / VP/Eicosene Copolymer [1,2,6] / Potassium Hydroxide [4]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Styrene/Acrylates Copolymer [1,4,6] / Butylene Glycol [1,2] / Diethylhexyl Syringylidenemalonate [2] / VP/Eicosene Copolymer [1,2,6] / 1,2-Hexandiol [1,2] / Potassium Hydroxide [4]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, 1;2-Hexandiol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1936,12 +1944,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>9 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (9%), Octisalate (4.5%)). 11 unknown ingredient(s) not in reference.</t>
+          <t>10 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769. Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1982,17 +1990,17 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (9%) [2] / Octisalate (4.5%) [2] / Octocrylene (9%) [2] / Styrene/Acrylates Copolymer [1,4,6] / Butylene Glycol [1,2] / Diethylhexyl Syringylidenemalonate [2] / VP/Eicosene Copolymer [1,2,6] / Potassium Hydroxide [4]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Styrene/Acrylates Copolymer [1,4,6] / Butylene Glycol [1,2] / Diethylhexyl Syringylidenemalonate [2] / VP/Eicosene Copolymer [1,2,6] / 1,2-Hexandiol [1,2] / Potassium Hydroxide [4]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, 1;2-Hexandiol, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2002,12 +2010,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>9 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (9%), Octisalate (4.5%)). 10 unknown ingredient(s) not in reference.</t>
+          <t>10 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962. Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2058,7 +2066,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2068,12 +2076,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the full retailer INCI list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol). 7 unknown ingredient(s) not in reference.</t>
+          <t>7 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849. Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Identical printed text on 1 other product(s): Sensitive Mineral SPF 50 Sunscreen. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2118,13 +2126,13 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Octocrylene (10%) [2] / Alcohol Denat. [4] (inferred: alcohol denat) / Butyloctyl Salicylate [2] / Silica [1,2] / Dimethicone [2,6] / Diethylhexyl Syringylidenemalonate [2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Alcohol Denat [4] (inferred: alcohol denat) / Butyloctyl Salicylate [2] / Silica [1,2] / Dimethicone [2,6] / Diethylhexyl Syringylidenemalonate [2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2134,12 +2142,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)). 18 unknown ingredient(s) not in reference.</t>
+          <t>11 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 18 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371. Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2184,13 +2192,13 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Octocrylene (10%) [2] / Alcohol Denat. [4] (inferred: alcohol denat) / Butyloctyl Salicylate [2] / Silica [1,2] / Dimethicone [2,6] / Diethylhexyl Syringylidenemalonate [2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Alcohol Denat [4] (inferred: alcohol denat) / Butyloctyl Salicylate [2] / Silica [1,2] / Dimethicone [2,6] / Diethylhexyl Syringylidenemalonate [2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2200,12 +2208,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)). 18 unknown ingredient(s) not in reference.</t>
+          <t>11 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 18 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848. Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2256,7 +2264,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2266,12 +2274,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the full retailer INCI list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol). 13 unknown ingredient(s) not in reference.</t>
+          <t>10 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195. Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2316,13 +2324,13 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (10%) [2] / Octisalate (5%) [2] / Octocrylene (10%) [2] / Alcohol Denat. [4] (inferred: alcohol denat) / Butyloctyl Salicylate [2] / Silica [1,2] / Diethylhexyl Syringylidenemalonate [2] / Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / 1,2-Hexanediol [1,2] / Iron Oxides [1,2,3]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Alcohol Denat [4] (inferred: alcohol denat) / Butyloctyl Salicylate [2] / Silica [1,2] / Diethylhexyl Syringylidenemalonate [2] / Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / 1,2-Hexanediol [1,2] / Iron Oxides [1,2,3]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Polyglyceryl-6 Behenate, Disodium EDTA</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Polyglyceryl-6 Behenate, Disodium EDTA</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2332,12 +2340,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13 flagged ingredient(s) in the full retailer INCI list (Avobenzone (3%), Homosalate (10%), Octisalate (5%)). 18 unknown ingredient(s) not in reference.</t>
+          <t>13 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 18 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307. Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2382,7 +2390,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Avobenzone (3%) [2] / Homosalate (7%) [2] / Octisalate (4.5%) [2] / Octocrylene (8%) [2]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -2390,12 +2398,12 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Avobenzone (3%), Homosalate (7%), Octisalate (4.5%)).</t>
+          <t>4 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. no retailer INCI found. No Eucerin Advanced Hydration SPF 30 spray listing on Walmart or Amazon (searched). Dermstore and CVS not yet checked. Tier without the PFAS rule: Avoid (Mild). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Eucerin Advanced Hydration SPF 30 spray found. The CVS brand shop lists only Sun Advanced Hydration SPF 50 Spray 6 oz (prodid 621595). Dermstore search for eucerin sunscreen spray spf 30 returned no Eucerin SPF 30 spray. Walmart and Amazon: no listing in round 1. Walgreens blocked; Ulta holding page. Unresolved.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2446,7 +2454,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Distarch Phosphate, Ceramide NP, Arginine HCl, Carnitine, Helianthus Annuus (Sunflower) Seed Oil</t>
+          <t>unknown — manual review needed: Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Distarch Phosphate, Ceramide NP, Carnitine, Helianthus Annuus (Sunflower) Seed Oil</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2456,12 +2464,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the full retailer INCI list (Dimethicone, Phenoxyethanol, Carbomer). 7 unknown ingredient(s) not in reference.</t>
+          <t>4 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082. Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2512,7 +2520,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Arginine HCL, Carnitine, Mannitol, Sucrose, Citrulline, Glycogen, Histidine HCL, Ceramide NP, Glutamic Acid, Lysine HCL</t>
+          <t>unknown — manual review needed: Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Carnitine, Mannitol, Sucrose, Citrulline, Glycogen, Ceramide NP, Glutamic Acid, Lysine HCL</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2522,12 +2530,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the full retailer INCI list (1,2-Hexanediol, Phenoxyethanol). 16 unknown ingredient(s) not in reference.</t>
+          <t>2 flagged ingredient(s) in the printed list (1,2-Hexanediol, Phenoxyethanol); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111. Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2564,32 +2572,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Pentylene Glycol [1,2]</t>
+          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Pentylene Glycol [1,2] / Decylene Glycol [1,2] (inferred: -glycol)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>colloidal oatmeal (2%)-, Sodium Cocoamphoacetate, C12-15 Alkyl Benzoate, Ceramide NP, Arginine HCl, Carnitine, Lauryl Glucoside, Decylene Glycol</t>
+          <t>unknown — manual review needed: colloidal oatmeal, Sodium Cocoamphoacetate, C12-15 Alkyl Benzoate, Ceramide NP, Carnitine, Lauryl Glucoside</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the full retailer INCI list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer). 8 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851. Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (Mild). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2640,7 +2648,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (1%), Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2650,12 +2658,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol). 5 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571. Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2700,24 +2708,24 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat)</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (1%), Glycyrrhiza Inflata Root Extract, Ceramide NP, Gellan Gum, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Glycyrrhiza Inflata Root Extract, Ceramide NP, Gellan Gum, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat.). 5 unknown ingredient(s) not in reference.</t>
+          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083. Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Use Caution. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2758,17 +2766,17 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
+          <t>Mineral Oil [1] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / Decylene Glycol [1,2] (inferred: -glycol) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / BHT [1,2]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (1%), Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Decylene Glycol, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA, BHT</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2778,12 +2786,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol). 9 unknown ingredient(s) not in reference.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, Decylene Glycol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674. Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674).</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2828,13 +2836,13 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Alcohol Denat. [4] (inferred: alcohol denat) / Laureth-9 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Pentylene Glycol [1,2] / Ethylhexylglycerin [4,5] / Carbomer [1,4,6]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Laureth-9 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Pentylene Glycol [1,2] / Ethylhexylglycerin [4,5] / Carbomer [1,4,6]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Menthol (0.1%), Hydrogenated Coco-Glycerides, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Arginine HCl, Ceramide NP, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Menthol, Hydrogenated Coco-Glycerides, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Ceramide NP, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2844,12 +2852,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the full retailer INCI list (Alcohol Denat., Laureth-9, Dimethicone). 13 unknown ingredient(s) not in reference.</t>
+          <t>7 flagged ingredient(s) in the printed list (Alcohol Denat, Laureth-9, Dimethicone); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664. Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2890,17 +2898,17 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Dimethicone [2,6] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6]</t>
+          <t>Mineral Oil [1] / Dimethicone [2,6] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / Phenoxyethanol [1,2,4,5,8] / 1-2-Hexanediol [1,2] / Carbomer [1,4,6] / Decylene Glycol [1,2] (inferred: -glycol)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Caprylic-Capric-Triglyceride, Colloidal Oatmeal, Methylpropanediol, 1-2-Hexanediol, Polyglyceryl-2 Caprate, Piroctone Olamine, Decylene Glycol</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2910,12 +2918,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, Dimethicone, PEG-40 Stearate). 7 unknown ingredient(s) not in reference.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149. Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2956,17 +2964,17 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Dimethicone [2,6] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6]</t>
+          <t>Mineral Oil [1] / Dimethicone [2,6] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Decylene Glycol [1,2] (inferred: -glycol)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate, Decylene Glycol</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2976,12 +2984,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, Dimethicone, PEG-40 Stearate). 5 unknown ingredient(s) not in reference.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299. Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3026,7 +3034,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Octisalate (3.5) [2]</t>
+          <t>Octisalate [2]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -3034,12 +3042,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Octisalate (3.5)).</t>
+          <t>1 flagged ingredient(s) in the printed list (Octisalate); tier applies to the printed subset only.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. no retailer INCI found. Walmart listing 912642578 prints no ingredient text; Amazon listings B082D8S4W3 and B00KIHJO3E print no ingredient text. Target not available in this session. Dermstore and CVS not yet checked. Tier without the PFAS rule: Use Caution. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Daily Hydration Broad Spectrum SPF 15 Body Lotion, 16.9 OZ (prodid 1013203) is not a clear match and not used. Its printed actives are Avobenzone 2.0%, Homosalate 3.4%, Octisalate 3.4%, Octocrylene 4.7%, while the brand key is Octisalate (3.5). The brand row is the Daily Protection SPF 15 moisturizer, a different product name. Walmart 912642578 and Amazon B082D8S4W3 / B00KIHJO3E print no ingredient text (round 1). Dermstore and Walgreens not usable. Unresolved.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3086,18 +3094,18 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Sunflower Seed oil</t>
+          <t>unknown — manual review needed: helianthus annuus (sunflower) seed oil</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 1 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. Candidate only, not used. Amazon listing is Eucerin Daily Hydration Lotion, Multipack, 3 x 16.9 fl oz. Its list contains Helianthus Annuus Seed Oil, matching the brand key ingredient (Sunflower Seed oil), but the multipack variant is not a clear match for the brand single product, and the brand prints no size. Candidate retailer list not used for grading: Amazon https://www.amazon.com/dp/B00AYSBR96. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3148,7 +3156,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3158,12 +3166,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the full retailer INCI list (Petrolatum, Mineral Oil, Phenoxyethanol). 3 unknown ingredient(s) not in reference.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Phenoxyethanol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749. Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749).</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3214,7 +3222,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3224,12 +3232,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, Propylene Glycol, Aluminum Stearates). 3 unknown ingredient(s) not in reference.</t>
+          <t>4 flagged ingredient(s) in the printed list (Mineral Oil, Propylene Glycol, Aluminum Stearates); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: heavy metals, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298. Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298).</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3276,18 +3284,18 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 1 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. Candidate only, not confirmed. Walmart Eucerin Baby Eczema Relief Hydrogel, 5 fl oz: its printed Ingredients field does not include Colloidal Oatmeal, the brand active, so the brand Colloidal Oatmeal, Water, Glycerin pattern cannot be confirmed. Water and Glycerin appear first. Candidate retailer list not used for grading: Walmart https://www.walmart.com/ip/Eucerin-Baby-Eczema-Hydrogel-5oz-Tube/13173618198. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3324,32 +3332,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Pentylene Glycol [1,2]</t>
+          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Pentylene Glycol [1,2] / Decylene Glycol [1,2] (inferred: -glycol)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>colloidal oatmeal (2%)-, Sodium Cocoamphoacetate, C12-15 Alkyl Benzoate, Ceramide NP, Arginine HCl, Carnitine, Lauryl Glucoside, Decylene Glycol</t>
+          <t>unknown — manual review needed: colloidal oatmeal, Sodium Cocoamphoacetate, C12-15 Alkyl Benzoate, Ceramide NP, Carnitine, Lauryl Glucoside</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the full retailer INCI list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer). 8 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271. Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (Mild). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271).</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3402,12 +3410,12 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed brand-site subset (no verified retailer list) (Sodium Myreth Sulfate).</t>
+          <t>1 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate); tier applies to the printed subset only.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. no retailer INCI found. Walmart 682440208 and 14819669289 print no ingredient text; Amazon B01G7L6YDW shows only shea butter and B0C4WG48N9 shows no list. Target not available in this session. Tier without the PFAS rule: Avoid (Mild). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No usable text. CVS brand shop and search returned no Eucerin Baby Wash and Shampoo. Amazon search returned only a third-party Awiaub pack of three (13.5 oz), not a clear match, not used. Walmart 682440208 and 14819669289 print no ingredient text (round 1). Walgreens blocked; Ulta holding page. Unresolved. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos).</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3458,7 +3466,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal (1%), Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3468,12 +3476,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the full retailer INCI list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol). 5 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Source: Walmart, https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944. Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Avoid (High Priority Swap). Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944).</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3520,18 +3528,18 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Dexpanthenol</t>
+          <t>unknown — manual review needed: Dexpanthenol</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed brand-site subset (no verified retailer list). 1 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Source: brand site (key or active ingredients only); no verified retailer list. Tier is provisional. Candidate only, not confirmed. Walmart Eucerin Baby Lotion, 13.5 fl oz, Fragrance Free lists Panthenol, the INCI name for the brand key ingredient Dexpanthenol. Brand printed only one key ingredient, so the first-ingredient cross-check cannot be done. Size not printed on brand listing. Candidate retailer list not used for grading: Walmart https://www.walmart.com/ip/Eucerin-Baby-Lotion-Fragrance-Free-13-5-fl-oz-Bottle/50463431. Unknown ingredients left unscored; tier does not account for them. Tier without the PFAS rule: Puberty Safe. Grading input removed Active/Inactive labels and % formatting; ingredients_verbatim unchanged.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -530,7 +530,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Hydrogenated Cocoglycerides, Butyrospermum Parkii (Shea) Butter, Ceramide NP, Carnitine, Carrageenan, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+          <t>unknown — manual review needed: Water, Glycerin, Urea, Hydrogenated Cocoglycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCI, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 19 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -596,7 +596,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: glyceryl glucoside, butyrospermum parkii (shea) butter, Methylpropanediol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Dimethiconol, Chondrus Crispus (Carrageenan), Carnitine, Ceramide 3, Mannitol, Sucrose, Citrulline, Glycogen, Glutamic Acid, Lysine HCL</t>
+          <t>unknown — manual review needed: Water, Glycerin, glyceryl glucoside, sodium lactate, butyrospermum parkii (shea) butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Arginine HCL, Sodium PCA, Dimethiconol, Lactic Acid, Chondrus Crispus (Carrageenan), Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Cyclomethicone, Sodium Cetearyl Sulfate, 1,2-Hexanediol); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Cyclomethicone, Sodium Cetearyl Sulfate, 1,2-Hexanediol); tier applies to the printed subset only. 27 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -662,7 +662,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: CERAMIDE 3, NATURAL MOISTURIZING FACTORS, Hydrogenated Coco-Glycerides, Butyl Adipate, Dicaprylyl Ether, Tapioca Starch, Ceramide NP, Carnitine, Helianthus Annuus (Sunflower) Seed Oil</t>
+          <t>unknown — manual review needed: NATURAL MOISTURIZING FACTORS, Water, Glycerin, Urea, Glyceryl Stearate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Dicaprylyl Ether, Sodium Lactate, Tapioca Starch, Lactic Acid, Sodium PCA, Arginine HCI, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 19 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -728,13 +728,13 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Sodium Cocoamphoacetate, Lauryl Glucoside, Diammonium Citrate, Sodium Acetate, Sodium Salicylate</t>
+          <t>unknown — manual review needed: Water, Sodium Cocoamphoacetate, Lauryl Glucoside, Glycerin, Diammonium Citrate, Sodium Acetate, Sodium Salicylate</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Glycol Distearate, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Glycol Distearate, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -790,7 +790,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Hydrogenated Coco-Glycerides, Butyrospermum Parkii (Shea) Butter, Ceramide NP, Carnitine, Carrageenan, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+          <t>unknown — manual review needed: Water, Glycerin, Urea, Hydrogenated Coco-Glycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCl, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 19 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -856,7 +856,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Diisopropyl Adipate, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Tapioca Starch, Pantolactone, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Water, Glycerin, Diisopropyl Adipate, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Tapioca Starch, Pantolactone, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -922,7 +922,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Water, Glycerin, Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, Dimethicone); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, Dimethicone); tier applies to the printed subset only. 19 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -988,22 +988,22 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Cocoglycerides, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Trisodium EDTA, Tin Oxide</t>
+          <t>unknown — manual review needed: Water, Glycerin, Caprylic/Capric Triglyceride, Cocoglycerides, Isopropyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Sodium Hydroxide, Trisodium EDTA, Tin Oxide</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Synthetic Fluorphlogopite, Phenoxyethanol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Synthetic Fluorphlogopite, Phenoxyethanol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. D2: iron oxides exempt from the heavy-metal (cat. 3) escalation. PFAS-treated escalation applied as written; pending practitioner confirmation. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1054,7 +1054,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Water, Glycerin, Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Sodium Stearoyl Glutamate, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1120,22 +1120,22 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA</t>
+          <t>unknown — manual review needed: Water, Glycerin, Glyceryl Stearate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>9 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>9 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. D1: unspecified silica does not trigger the PFAS-treated escalation. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1186,7 +1186,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate</t>
+          <t>unknown — manual review needed: Water, Glycerin, Butyrospermum Parkii (Shea) Butter, Cetearyl Isononanoate, Isopropyl Palmitate, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1252,13 +1252,13 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Sodium Cocoamphoacetate, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside</t>
+          <t>unknown — manual review needed: Water, Sodium Cocoamphoacetate, Glycerin, Coco-Betaine, Lactic Acid, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference.</t>
+          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1314,7 +1314,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Distarch Phosphate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum</t>
+          <t>unknown — manual review needed: Water, Glycerin, Distarch Phosphate, Cetearyl Isononanoate, Isopropyl Palmitate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum, Lactic Acid</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1380,7 +1380,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: Water, Glycerin, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1442,13 +1442,13 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Water, Glycerin, Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 3 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 7 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1500,13 +1500,13 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Water, Glycerin, Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 3 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 7 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1562,7 +1562,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Methoxy PEG-22/Dodecyl Glycol Copolymer, Sorbitan Isostearate</t>
+          <t>unknown — manual review needed: Water, Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Glycerin, Methoxy PEG-22/Dodecyl Glycol Copolymer, Lactic Acid, Ozokerite, Sorbitan Isostearate, Hydrogenated Castor Oil</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-7 Hydrogenated Castor Oil, Dimethicone); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-7 Hydrogenated Castor Oil, Dimethicone); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1802,7 +1802,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1868,22 +1868,22 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: l-6 Stearate, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Polyglyceryl-6 Behenate, Disodium EDTA</t>
+          <t>unknown — manual review needed: l-6 Stearate, Glycerin, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Glyceryl Stearate, Polyglyceryl-6 Behenate, Disodium EDTA</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>8 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. D1: unspecified silica does not trigger the PFAS-treated escalation. Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1934,7 +1934,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: Water, Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2000,7 +2000,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2066,7 +2066,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2132,7 +2132,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Glycerin, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 18 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 20 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2198,7 +2198,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Glycerin, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 18 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 20 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2264,22 +2264,22 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate</t>
+          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. D1: unspecified silica does not trigger the PFAS-treated escalation. D2: iron oxides exempt from the heavy-metal (cat. 3) escalation. PFAS-treated escalation applied as written; pending practitioner confirmation. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2330,22 +2330,22 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Polyglyceryl-6 Behenate, Disodium EDTA</t>
+          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Glycerin, Polyglyceryl-6 Behenate, Sodium Polyacrylate, Disodium EDTA</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 18 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>13 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 21 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. D1: unspecified silica does not trigger the PFAS-treated escalation. D2: iron oxides exempt from the heavy-metal (cat. 3) escalation. PFAS-treated escalation applied as written; pending practitioner confirmation. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2454,7 +2454,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Distarch Phosphate, Ceramide NP, Carnitine, Helianthus Annuus (Sunflower) Seed Oil</t>
+          <t>unknown — manual review needed: Water, Urea, Glycerin, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Sodium Lactate, Distarch Phosphate, Lactic Acid, Sodium PCA, Arginine HCl, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 18 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2520,7 +2520,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Carnitine, Mannitol, Sucrose, Citrulline, Glycogen, Ceramide NP, Glutamic Acid, Lysine HCL</t>
+          <t>unknown — manual review needed: Water, Urea, Glycerin, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Arginine HCL, Sodium PCA, Lactic Acid, Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (1,2-Hexanediol, Phenoxyethanol); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (1,2-Hexanediol, Phenoxyethanol); tier applies to the printed subset only. 24 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2586,13 +2586,13 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: colloidal oatmeal, Sodium Cocoamphoacetate, C12-15 Alkyl Benzoate, Ceramide NP, Carnitine, Lauryl Glucoside</t>
+          <t>unknown — manual review needed: colloidal oatmeal, Water, Isopropyl Palmitate, Glycerin, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2648,7 +2648,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Water, Glycerin, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2714,13 +2714,13 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Glycyrrhiza Inflata Root Extract, Ceramide NP, Gellan Gum, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Water, Glycerin, Octyldodecanol, Caprylic/Capric Triglyceride, Glycyrrhiza Inflata Root Extract, Phytosphingosine, Gellan Gum, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference.</t>
+          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2776,7 +2776,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Water, Glycerin, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Glycyrrhiza Inflata Root Extract, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, Decylene Glycol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, Decylene Glycol); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2842,7 +2842,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Menthol, Hydrogenated Coco-Glycerides, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Ceramide NP, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Menthol, Water, Glycerin, Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Glyceryl Stearate, Arginine HCl, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Sodium Hydroxide, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Alcohol Denat, Laureth-9, Dimethicone); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Alcohol Denat, Laureth-9, Dimethicone); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2908,7 +2908,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Water, Glycerin, caprylic/capric triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2974,7 +2974,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate</t>
+          <t>unknown — manual review needed: Water, Glycerin, Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3156,7 +3156,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Water, Ceresin, Lanolin Alcohol, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Phenoxyethanol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Phenoxyethanol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3222,7 +3222,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Water, Isopropyl Palmitate, Sorbitol, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Mineral Oil, Propylene Glycol, Aluminum Stearates); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: heavy metals, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Mineral Oil, Propylene Glycol, Aluminum Stearates); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: heavy metals, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3284,13 +3284,13 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Water, Glycerin</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 3 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3346,13 +3346,13 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: colloidal oatmeal, Sodium Cocoamphoacetate, C12-15 Alkyl Benzoate, Ceramide NP, Carnitine, Lauryl Glucoside</t>
+          <t>unknown — manual review needed: colloidal oatmeal, Water, Isopropyl Palmitate, Glycerin, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3406,11 +3406,15 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Water</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate); tier applies to the printed subset only.</t>
+          <t>1 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3466,7 +3470,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glycyrrhiza Inflata Root Extract, Ceramide NP, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Water, Glycerin, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3476,7 +3480,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -993,17 +993,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Synthetic Fluorphlogopite, Phenoxyethanol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Synthetic Fluorphlogopite, Phenoxyethanol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. D2: iron oxides exempt from the heavy-metal (cat. 3) escalation. PFAS-treated escalation applied as written; pending practitioner confirmation. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. D1: unspecified silica does not trigger the PFAS-treated escalation. D2: iron oxides exempt from the heavy-metal (cat. 3) escalation. PFAS-treated escalation applied as written; pending practitioner confirmation. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2335,17 +2335,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 21 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>13 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 21 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. D1: unspecified silica does not trigger the PFAS-treated escalation. D2: iron oxides exempt from the heavy-metal (cat. 3) escalation. PFAS-treated escalation applied as written; pending practitioner confirmation. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -530,7 +530,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Urea, Hydrogenated Cocoglycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCI, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+          <t>unknown — manual review needed: Urea, Hydrogenated Cocoglycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCI, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -540,17 +540,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 19 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). Ingredient source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Urea, Hydrogenated Cocoglycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCI, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer. Ingredient source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -596,7 +596,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, glyceryl glucoside, sodium lactate, butyrospermum parkii (shea) butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Arginine HCL, Sodium PCA, Dimethiconol, Lactic Acid, Chondrus Crispus (Carrageenan), Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL</t>
+          <t>unknown — manual review needed: glyceryl glucoside, sodium lactate, butyrospermum parkii (shea) butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Arginine HCL, Sodium PCA, Dimethiconol, Lactic Acid, Chondrus Crispus (Carrageenan), Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Cyclomethicone, Sodium Cetearyl Sulfate, 1,2-Hexanediol); tier applies to the printed subset only. 27 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 25 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: glyceryl glucoside, sodium lactate, butyrospermum parkii (shea) butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Arginine HCL, Sodium PCA, Dimethiconol, Lactic Acid, Chondrus Crispus (Carrageenan), Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -662,7 +662,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: NATURAL MOISTURIZING FACTORS, Water, Glycerin, Urea, Glyceryl Stearate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Dicaprylyl Ether, Sodium Lactate, Tapioca Starch, Lactic Acid, Sodium PCA, Arginine HCI, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil</t>
+          <t>unknown — manual review needed: NATURAL MOISTURIZING FACTORS, Urea, Glyceryl Stearate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Dicaprylyl Ether, Sodium Lactate, Tapioca Starch, Lactic Acid, Sodium PCA, Arginine HCI, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 19 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: NATURAL MOISTURIZING FACTORS, Urea, Glyceryl Stearate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Dicaprylyl Ether, Sodium Lactate, Tapioca Starch, Lactic Acid, Sodium PCA, Arginine HCI, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Avoid (Moderate)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -728,23 +728,23 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Sodium Cocoamphoacetate, Lauryl Glucoside, Glycerin, Diammonium Citrate, Sodium Acetate, Sodium Salicylate</t>
+          <t>unknown — manual review needed: Sodium Cocoamphoacetate, Lauryl Glucoside, Diammonium Citrate, Sodium Acetate, Sodium Salicylate</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Glycol Distearate, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 5 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sodium Cocoamphoacetate, Lauryl Glucoside, Diammonium Citrate, Sodium Acetate, Sodium Salicylate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -790,7 +790,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Urea, Hydrogenated Coco-Glycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCl, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+          <t>unknown — manual review needed: Urea, Hydrogenated Coco-Glycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCl, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -800,17 +800,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 19 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Urea, Hydrogenated Coco-Glycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCl, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -856,7 +856,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Diisopropyl Adipate, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Tapioca Starch, Pantolactone, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Diisopropyl Adipate, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Tapioca Starch, Pantolactone, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 15 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Diisopropyl Adipate, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Tapioca Starch, Pantolactone, Trisodium EDTA. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -922,7 +922,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -932,17 +932,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, Dimethicone); tier applies to the printed subset only. 19 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -988,7 +988,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Caprylic/Capric Triglyceride, Cocoglycerides, Isopropyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Sodium Hydroxide, Trisodium EDTA, Tin Oxide</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Cocoglycerides, Isopropyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Sodium Hydroxide, Trisodium EDTA, Tin Oxide</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Synthetic Fluorphlogopite, Phenoxyethanol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 13 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Cocoglycerides, Isopropyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Sodium Hydroxide, Trisodium EDTA, Tin Oxide. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1054,7 +1054,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Sodium Stearoyl Glutamate, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Sodium Stearoyl Glutamate, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. Ingredient source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Sodium Stearoyl Glutamate, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1120,7 +1120,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Glyceryl Stearate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA</t>
+          <t>unknown — manual review needed: Glyceryl Stearate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1130,17 +1130,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>9 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 9. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. D1: unspecified silica does not trigger the PFAS-treated escalation. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Glyceryl Stearate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1186,7 +1186,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Butyrospermum Parkii (Shea) Butter, Cetearyl Isononanoate, Isopropyl Palmitate, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate</t>
+          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter, Cetearyl Isononanoate, Isopropyl Palmitate, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1196,17 +1196,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Cetearyl Isononanoate, Isopropyl Palmitate, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1252,23 +1252,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Sodium Cocoamphoacetate, Glycerin, Coco-Betaine, Lactic Acid, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside, Sodium Hydroxide</t>
+          <t>unknown — manual review needed: Sodium Cocoamphoacetate, Coco-Betaine, Lactic Acid, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sodium Cocoamphoacetate, Coco-Betaine, Lactic Acid, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1314,7 +1314,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Distarch Phosphate, Cetearyl Isononanoate, Isopropyl Palmitate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum, Lactic Acid</t>
+          <t>unknown — manual review needed: Distarch Phosphate, Cetearyl Isononanoate, Isopropyl Palmitate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum, Lactic Acid</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. Ingredient source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Distarch Phosphate, Cetearyl Isononanoate, Isopropyl Palmitate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum, Lactic Acid. Ingredient source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1380,7 +1380,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1442,23 +1442,23 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 7 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 5 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 6.8 FL OZ. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 6.8 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1500,23 +1500,23 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 7 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 5 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 13.5 FL OZ. Ingredient source: Amazon (https://www.amazon.com/dp/B094NWLKKZ).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 13.5 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA. Ingredient source: Amazon (https://www.amazon.com/dp/B094NWLKKZ).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1562,7 +1562,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Glycerin, Methoxy PEG-22/Dodecyl Glycol Copolymer, Lactic Acid, Ozokerite, Sorbitan Isostearate, Hydrogenated Castor Oil</t>
+          <t>unknown — manual review needed: Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Methoxy PEG-22/Dodecyl Glycol Copolymer, Lactic Acid, Ozokerite, Sorbitan Isostearate, Hydrogenated Castor Oil</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-7 Hydrogenated Castor Oil, Dimethicone); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Methoxy PEG-22/Dodecyl Glycol Copolymer, Lactic Acid, Ozokerite, Sorbitan Isostearate, Hydrogenated Castor Oil. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1630,12 +1630,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Q10.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1688,12 +1688,12 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 2 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Q10, Shea Butter.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1746,12 +1746,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 2 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Glycyrrhetinic Acid, Licochalcone A.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1802,7 +1802,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1868,7 +1868,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: l-6 Stearate, Glycerin, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Glyceryl Stearate, Polyglyceryl-6 Behenate, Disodium EDTA</t>
+          <t>unknown — manual review needed: l-6 Stearate, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Glyceryl Stearate, Polyglyceryl-6 Behenate, Disodium EDTA</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. D1: unspecified silica does not trigger the PFAS-treated escalation. Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: l-6 Stearate, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Glyceryl Stearate, Polyglyceryl-6 Behenate, Disodium EDTA. Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1934,7 +1934,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1944,17 +1944,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2000,7 +2000,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2066,7 +2066,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Identical printed text on 1 other product(s): Sensitive Mineral SPF 50 Sunscreen. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Identical printed text on 1 other product(s): Sensitive Mineral SPF 50 Sunscreen. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2132,7 +2132,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Glycerin, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2142,17 +2142,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 20 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 18 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2198,7 +2198,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Glycerin, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 20 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 18 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2264,7 +2264,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2274,17 +2274,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2330,7 +2330,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Glycerin, Polyglyceryl-6 Behenate, Sodium Polyacrylate, Disodium EDTA</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Polyglyceryl-6 Behenate, Sodium Polyacrylate, Disodium EDTA</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2340,17 +2340,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 21 unknown ingredient(s) not in reference. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 19 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 13. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Polyglyceryl-6 Behenate, Sodium Polyacrylate, Disodium EDTA. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2454,7 +2454,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Urea, Glycerin, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Sodium Lactate, Distarch Phosphate, Lactic Acid, Sodium PCA, Arginine HCl, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil</t>
+          <t>unknown — manual review needed: Urea, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Sodium Lactate, Distarch Phosphate, Lactic Acid, Sodium PCA, Arginine HCl, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2464,17 +2464,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 18 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 16 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Urea, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Sodium Lactate, Distarch Phosphate, Lactic Acid, Sodium PCA, Arginine HCl, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2520,7 +2520,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Urea, Glycerin, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Arginine HCL, Sodium PCA, Lactic Acid, Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL</t>
+          <t>unknown — manual review needed: Urea, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Arginine HCL, Sodium PCA, Lactic Acid, Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2530,17 +2530,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (1,2-Hexanediol, Phenoxyethanol); tier applies to the printed subset only. 24 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 22 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Urea, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Arginine HCL, Sodium PCA, Lactic Acid, Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Avoid (Moderate)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2586,23 +2586,23 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: colloidal oatmeal, Water, Isopropyl Palmitate, Glycerin, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide</t>
+          <t>unknown — manual review needed: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2648,7 +2648,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Water, Glycerin, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2714,23 +2714,23 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Water, Glycerin, Octyldodecanol, Caprylic/Capric Triglyceride, Glycyrrhiza Inflata Root Extract, Phytosphingosine, Gellan Gum, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Octyldodecanol, Caprylic/Capric Triglyceride, Glycyrrhiza Inflata Root Extract, Phytosphingosine, Gellan Gum, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Colloidal Oatmeal, Octyldodecanol, Caprylic/Capric Triglyceride, Glycyrrhiza Inflata Root Extract, Phytosphingosine, Gellan Gum, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2776,7 +2776,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Water, Glycerin, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Glycyrrhiza Inflata Root Extract, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Glycyrrhiza Inflata Root Extract, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2786,17 +2786,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, Decylene Glycol); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Glycyrrhiza Inflata Root Extract, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674).</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2842,7 +2842,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Menthol, Water, Glycerin, Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Glyceryl Stearate, Arginine HCl, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Sodium Hydroxide, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Menthol, Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Glyceryl Stearate, Arginine HCl, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Sodium Hydroxide, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Alcohol Denat, Laureth-9, Dimethicone); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 15 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Menthol, Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Glyceryl Stearate, Arginine HCl, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Sodium Hydroxide, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2908,7 +2908,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, caprylic/capric triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate, Piroctone Olamine</t>
+          <t>unknown — manual review needed: caprylic/capric triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2918,17 +2918,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: caprylic/capric triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2974,7 +2974,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2984,17 +2984,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -3100,12 +3100,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: helianthus annuus (sunflower) seed oil.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -3156,7 +3156,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Ceresin, Lanolin Alcohol, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Phenoxyethanol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 3 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749).</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -3222,7 +3222,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Isopropyl Palmitate, Sorbitol, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Isopropyl Palmitate, Sorbitol, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3232,17 +3232,17 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Mineral Oil, Propylene Glycol, Aluminum Stearates); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: heavy metals, carcinogen in leave-on.</t>
+          <t>Ungradable: 5 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: heavy metals, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Isopropyl Palmitate, Sorbitol, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298).</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -3284,18 +3284,18 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Water, Glycerin</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 3 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Colloidal Oatmeal.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Avoid (Moderate)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3346,23 +3346,23 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: colloidal oatmeal, Water, Isopropyl Palmitate, Glycerin, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide</t>
+          <t>unknown — manual review needed: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271).</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -3406,15 +3406,11 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>unknown — manual review needed: Water</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference.</t>
+          <t>1 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate); tier applies to the printed subset only.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3456,7 +3452,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3470,7 +3466,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Water, Glycerin, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3480,17 +3476,17 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944).</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3518,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3538,12 +3534,12 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Dexpanthenol.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -540,12 +540,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Urea, Hydrogenated Cocoglycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCI, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer. Ingredient source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Urea, Hydrogenated Cocoglycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCI, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer. Ingredient source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ungradable: 25 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 25 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: glyceryl glucoside, sodium lactate, butyrospermum parkii (shea) butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Arginine HCL, Sodium PCA, Dimethiconol, Lactic Acid, Chondrus Crispus (Carrageenan), Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: glyceryl glucoside, sodium lactate, butyrospermum parkii (shea) butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Arginine HCL, Sodium PCA, Dimethiconol, Lactic Acid, Chondrus Crispus (Carrageenan), Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: NATURAL MOISTURIZING FACTORS, Urea, Glyceryl Stearate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Dicaprylyl Ether, Sodium Lactate, Tapioca Starch, Lactic Acid, Sodium PCA, Arginine HCI, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: NATURAL MOISTURIZING FACTORS, Urea, Glyceryl Stearate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Dicaprylyl Ether, Sodium Lactate, Tapioca Starch, Lactic Acid, Sodium PCA, Arginine HCI, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -734,12 +734,12 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ungradable: 5 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
+          <t>Ungradable: 5 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sodium Cocoamphoacetate, Lauryl Glucoside, Diammonium Citrate, Sodium Acetate, Sodium Salicylate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sodium Cocoamphoacetate, Lauryl Glucoside, Diammonium Citrate, Sodium Acetate, Sodium Salicylate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Urea, Hydrogenated Coco-Glycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCl, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Urea, Hydrogenated Coco-Glycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCl, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ungradable: 15 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 15 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Diisopropyl Adipate, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Tapioca Starch, Pantolactone, Trisodium EDTA. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Diisopropyl Adipate, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Tapioca Starch, Pantolactone, Trisodium EDTA. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ungradable: 13 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 13 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Cocoglycerides, Isopropyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Sodium Hydroxide, Trisodium EDTA, Tin Oxide. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Cocoglycerides, Isopropyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Sodium Hydroxide, Trisodium EDTA, Tin Oxide. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Sodium Stearoyl Glutamate, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Sodium Stearoyl Glutamate, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 9. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Glyceryl Stearate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Glyceryl Stearate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Cetearyl Isononanoate, Isopropyl Palmitate, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Cetearyl Isononanoate, Isopropyl Palmitate, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1258,12 +1258,12 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sodium Cocoamphoacetate, Coco-Betaine, Lactic Acid, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sodium Cocoamphoacetate, Coco-Betaine, Lactic Acid, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Distarch Phosphate, Cetearyl Isononanoate, Isopropyl Palmitate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum, Lactic Acid. Ingredient source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Distarch Phosphate, Cetearyl Isononanoate, Isopropyl Palmitate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum, Lactic Acid. Ingredient source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D8: one unknown ingredient, Use Caution floor applied (Sodium Ascorbyl Phosphate). Higher tier from other flags kept. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ungradable: 5 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>Ungradable: 5 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 6.8 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 6.8 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1506,12 +1506,12 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ungradable: 5 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>Ungradable: 5 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 13.5 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA. Ingredient source: Amazon (https://www.amazon.com/dp/B094NWLKKZ).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 13.5 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA. Ingredient source: Amazon (https://www.amazon.com/dp/B094NWLKKZ).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Methoxy PEG-22/Dodecyl Glycol Copolymer, Lactic Acid, Ozokerite, Sorbitan Isostearate, Hydrogenated Castor Oil. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Methoxy PEG-22/Dodecyl Glycol Copolymer, Lactic Acid, Ozokerite, Sorbitan Isostearate, Hydrogenated Castor Oil. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1630,12 +1630,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Q10.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. D8: one unknown ingredient, Use Caution floor applied (Q10).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1688,12 +1688,12 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Q10, Shea Butter.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. D7: ungradable. Two or more unknown ingredients remain: Q10, Shea Butter.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1746,12 +1746,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Glycyrrhetinic Acid, Licochalcone A.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row. D7: ungradable. Two or more unknown ingredients remain: Glycyrrhetinic Acid, Licochalcone A.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: l-6 Stearate, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Glyceryl Stearate, Polyglyceryl-6 Behenate, Disodium EDTA. Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: l-6 Stearate, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Glyceryl Stearate, Polyglyceryl-6 Behenate, Disodium EDTA. Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. D7: ungradable. Two or more unknown ingredients remain: Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Identical printed text on 1 other product(s): Sensitive Mineral SPF 50 Sunscreen. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Identical printed text on 1 other product(s): Sensitive Mineral SPF 50 Sunscreen. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ungradable: 18 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 18 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ungradable: 18 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 18 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Ungradable: 19 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 13. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 19 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 13. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Polyglyceryl-6 Behenate, Sodium Polyacrylate, Disodium EDTA. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Polyglyceryl-6 Behenate, Sodium Polyacrylate, Disodium EDTA. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Ungradable: 16 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 16 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Urea, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Sodium Lactate, Distarch Phosphate, Lactic Acid, Sodium PCA, Arginine HCl, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Urea, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Sodium Lactate, Distarch Phosphate, Lactic Acid, Sodium PCA, Arginine HCl, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ungradable: 22 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 22 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Urea, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Arginine HCL, Sodium PCA, Lactic Acid, Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Urea, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Arginine HCL, Sodium PCA, Lactic Acid, Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2592,12 +2592,12 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2720,12 +2720,12 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Colloidal Oatmeal, Octyldodecanol, Caprylic/Capric Triglyceride, Glycyrrhiza Inflata Root Extract, Phytosphingosine, Gellan Gum, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Colloidal Oatmeal, Octyldodecanol, Caprylic/Capric Triglyceride, Glycyrrhiza Inflata Root Extract, Phytosphingosine, Gellan Gum, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Glycyrrhiza Inflata Root Extract, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Glycyrrhiza Inflata Root Extract, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674).</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ungradable: 15 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 15 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Menthol, Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Glyceryl Stearate, Arginine HCl, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Sodium Hydroxide, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Menthol, Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Glyceryl Stearate, Arginine HCl, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Sodium Hydroxide, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: caprylic/capric triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: caprylic/capric triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -3100,12 +3100,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: helianthus annuus (sunflower) seed oil.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. D8: one unknown ingredient, Use Caution floor applied (helianthus annuus (sunflower) seed oil).</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749).</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Ungradable: 5 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: heavy metals, carcinogen in leave-on.</t>
+          <t>Ungradable: 5 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: heavy metals, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Isopropyl Palmitate, Sorbitol, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D7: ungradable. Two or more unknown ingredients remain: Isopropyl Palmitate, Sorbitol, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298).</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -3290,12 +3290,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Colloidal Oatmeal.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D8: one unknown ingredient, Use Caution floor applied (Colloidal Oatmeal).</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3352,12 +3352,12 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271).</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944).</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3534,12 +3534,12 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Dexpanthenol.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. D8: one unknown ingredient, Use Caution floor applied (Dexpanthenol).</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1630,12 +1630,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: source text unresolved (practitioner exception, 2026-10-17). Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. D8: one unknown ingredient, Use Caution floor applied (Q10).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Q10.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -3042,12 +3042,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Octisalate); tier applies to the printed subset only.</t>
+          <t>Ungradable: source text unresolved (practitioner exception, 2026-10-17). Partial flags recorded: 1.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Daily Hydration Broad Spectrum SPF 15 Body Lotion, 16.9 OZ (prodid 1013203) is not a clear match and not used. Its printed actives are Avobenzone 2.0%, Homosalate 3.4%, Octisalate 3.4%, Octocrylene 4.7%, while the brand key is Octisalate (3.5). The brand row is the Daily Protection SPF 15 moisturizer, a different product name. Walmart 912642578 and Amazon B082D8S4W3 / B00KIHJO3E print no ingredient text (round 1). Dermstore and Walgreens not usable. Unresolved.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Daily Hydration Broad Spectrum SPF 15 Body Lotion, 16.9 OZ (prodid 1013203) is not a clear match and not used. Its printed actives are Avobenzone 2.0%, Homosalate 3.4%, Octisalate 3.4%, Octocrylene 4.7%, while the brand key is Octisalate (3.5). The brand row is the Daily Protection SPF 15 moisturizer, a different product name. Walmart 912642578 and Amazon B082D8S4W3 / B00KIHJO3E print no ingredient text (round 1). Dermstore and Walgreens not usable. Unresolved. Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3).</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -3100,12 +3100,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: source text unresolved (practitioner exception, 2026-10-17). Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. D8: one unknown ingredient, Use Caution floor applied (helianthus annuus (sunflower) seed oil).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: helianthus annuus (sunflower) seed oil.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -3290,12 +3290,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: source text unresolved (practitioner exception, 2026-10-17). Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D8: one unknown ingredient, Use Caution floor applied (Colloidal Oatmeal).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Colloidal Oatmeal.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3534,12 +3534,12 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: source text unresolved (practitioner exception, 2026-10-17). Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. D8: one unknown ingredient, Use Caution floor applied (Dexpanthenol).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Dexpanthenol.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -540,17 +540,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Urea, Hydrogenated Cocoglycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCI, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer. Ingredient source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -606,12 +606,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ungradable: 25 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Cyclomethicone, Sodium Cetearyl Sulfate, 1,2-Hexanediol); tier applies to the printed subset only. 25 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: glyceryl glucoside, sodium lactate, butyrospermum parkii (shea) butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Arginine HCL, Sodium PCA, Dimethiconol, Lactic Acid, Chondrus Crispus (Carrageenan), Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 25 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -672,17 +672,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: NATURAL MOISTURIZING FACTORS, Urea, Glyceryl Stearate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Dicaprylyl Ether, Sodium Lactate, Tapioca Starch, Lactic Acid, Sodium PCA, Arginine HCI, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -734,17 +734,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ungradable: 5 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Glycol Distearate, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sodium Cocoamphoacetate, Lauryl Glucoside, Diammonium Citrate, Sodium Acetate, Sodium Salicylate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -800,17 +800,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Urea, Hydrogenated Coco-Glycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCl, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -866,17 +866,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ungradable: 15 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Diisopropyl Adipate, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Tapioca Starch, Pantolactone, Trisodium EDTA. Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -932,17 +932,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, Dimethicone); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -998,17 +998,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ungradable: 13 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Synthetic Fluorphlogopite, Phenoxyethanol); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Cocoglycerides, Isopropyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Sodium Hydroxide, Trisodium EDTA, Tin Oxide. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Sodium Stearoyl Glutamate, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1130,17 +1130,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: carcinogen in leave-on.</t>
+          <t>9 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Glyceryl Stearate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1196,17 +1196,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Cetearyl Isononanoate, Isopropyl Palmitate, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1258,17 +1258,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1.</t>
+          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Sodium Cocoamphoacetate, Coco-Betaine, Lactic Acid, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Distarch Phosphate, Cetearyl Isononanoate, Isopropyl Palmitate, Squalene, Gellan Gum, Carrageenan, Pantolactone, Glycine Soja (Soybean) Oil, Dehydroxanthan Gum, Lactic Acid. Ingredient source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, PEG-40 Hydrogenated Castor Oil); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D8: one unknown ingredient, Use Caution floor applied (Sodium Ascorbyl Phosphate). Higher tier from other flags kept. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1448,17 +1448,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ungradable: 5 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 5 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 6.8 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 6.8 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1506,17 +1506,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ungradable: 5 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 5 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 13.5 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA. Ingredient source: Amazon (https://www.amazon.com/dp/B094NWLKKZ).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 13.5 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Amazon (https://www.amazon.com/dp/B094NWLKKZ).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-7 Hydrogenated Castor Oil, Dimethicone); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Methoxy PEG-22/Dodecyl Glycol Copolymer, Lactic Acid, Ozokerite, Sorbitan Isostearate, Hydrogenated Castor Oil. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Q10.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Q10.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Puberty Safe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1688,12 +1688,12 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 2 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. D7: ungradable. Two or more unknown ingredients remain: Q10, Shea Butter.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Puberty Safe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1746,12 +1746,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 2 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row. D7: ungradable. Two or more unknown ingredients remain: Glycyrrhetinic Acid, Licochalcone A.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: carcinogen in leave-on.</t>
+          <t>8 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: l-6 Stearate, Silica Dimethyl Silylate, Tapioca Starch, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Copernicia Cerifera (Carnauba) Wax, Hydroxypropyl Methylcellulose, Glyceryl Stearate, Polyglyceryl-6 Behenate, Disodium EDTA. Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1944,17 +1944,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. D7: ungradable. Two or more unknown ingredients remain: Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Aloe Barbadensis Leaf Juice, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Identical printed text on 1 other product(s): Sensitive Mineral SPF 50 Sunscreen. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Identical printed text on 1 other product(s): Sensitive Mineral SPF 50 Sunscreen. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2142,17 +2142,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ungradable: 18 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 18 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 18 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ungradable: 18 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 18 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 18 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2274,17 +2274,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Butyloctyl Salicylate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2340,17 +2340,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Ungradable: 19 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 13. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>13 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 19 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Polyglyceryl-6 Behenate, Sodium Polyacrylate, Disodium EDTA. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 19 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2464,17 +2464,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Ungradable: 16 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Urea, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Sodium Lactate, Distarch Phosphate, Lactic Acid, Sodium PCA, Arginine HCl, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2530,17 +2530,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ungradable: 22 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (1,2-Hexanediol, Phenoxyethanol); tier applies to the printed subset only. 22 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Urea, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Arginine HCL, Sodium PCA, Lactic Acid, Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 22 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2592,17 +2592,17 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2720,17 +2720,17 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1.</t>
+          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Colloidal Oatmeal, Octyldodecanol, Caprylic/Capric Triglyceride, Glycyrrhiza Inflata Root Extract, Phytosphingosine, Gellan Gum, Hydroxyacetophenone. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2786,17 +2786,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, Decylene Glycol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Glycyrrhiza Inflata Root Extract, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674).</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ungradable: 15 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Alcohol Denat, Laureth-9, Dimethicone); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Menthol, Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Triisostearin, Palmitic Acid, Stearic Acid, Distarch Phosphate, Glyceryl Stearate, Arginine HCl, Myristic Acid, Arachidic Acid, 4-t-butylcyclohexanol, Menthoxypropanediol, Sodium Hydroxide, Trisodium EDTA. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2918,17 +2918,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: caprylic/capric triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2984,17 +2984,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: helianthus annuus (sunflower) seed oil.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: helianthus annuus (sunflower) seed oil.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Phenoxyethanol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. 3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749).</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -3232,17 +3232,17 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Ungradable: 5 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: heavy metals, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Mineral Oil, Propylene Glycol, Aluminum Stearates); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D7: ungradable. Two or more unknown ingredients remain: Isopropyl Palmitate, Sorbitol, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Lanolin Alcohol. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). 5 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298).</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Colloidal Oatmeal.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Colloidal Oatmeal.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3352,17 +3352,17 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271).</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944).</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Dexpanthenol.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Dexpanthenol.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 25 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 25 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from flags (2026-10-17). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 1 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 6.8 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 6.8 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 13.5 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Amazon (https://www.amazon.com/dp/B094NWLKKZ).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 13.5 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Amazon (https://www.amazon.com/dp/B094NWLKKZ).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Q10.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. 1 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 1 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Q10.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. 2 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 2 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row. 2 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 2 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion. 8 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Identical printed text on 1 other product(s): Sensitive Mineral SPF 50 Sunscreen. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Identical printed text on 1 other product(s): Sensitive Mineral SPF 50 Sunscreen. 8 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 18 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 18 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 18 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 18 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 14 unknown ingredient(s) excluded from flags (2026-10-17). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 19 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 19 unknown ingredient(s) excluded from flags (2026-10-17). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 22 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 22 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674).</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: helianthus annuus (sunflower) seed oil.</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. 1 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 1 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: helianthus annuus (sunflower) seed oil.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. 3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. 3 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749).</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). 5 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298).</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Colloidal Oatmeal.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 1 unknown ingredient(s) excluded from flags (2026-10-17). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Colloidal Oatmeal.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271).</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944).</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Dexpanthenol.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. 1 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 1 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Dexpanthenol.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1685,15 +1685,19 @@
           <t>unknown — manual review needed: Q10, Shea Butter</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>paraben or DMDM hydantoin</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 2 unknown ingredient(s) not in reference, excluded from grade.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. 2 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 2 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule).</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. Paraben/DMDM rule source: CVS 1.7 OZ (https://www.cvs.com/shop/ingredients/eucerin-sensitive-skin-experts-q10-anti-wrinkle-face-creme-1-7-oz-prodid-361289) (practitioner directive 2026-10-17). The brand's own printed text is 'Q10, Shea Butter' and does not include them; the variant match is not confirmed, so the tier rests on the retailer listing. 2 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 2 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule). Practitioner rule (2026-10-17): tier set from the retailer listing (METHYLPARABEN, ETHYLPARABEN, PROPYLPARABEN, BUTYLPARABEN, ISOBUTYLPARABEN, DMDM HYDANTOIN). The brand's printed text does not include them.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Q10, Shea Butter</t>
+          <t>Water, Glycerin, Ethylhexyl Cocoate, Hydrogenated Coco-Glycerides, Stearyl Alcohol, Butylene Glycol, Cetyl Alcohol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Glyceryl Stearate Citrate, Octyldodecanol, Tocopheryl Acetate, Ubiquinone, Biotin, Biosaccharide Gum-1, Sodium Ascorbyl Phosphate, Zea Mays (Corn) Oil, Beta-Carotene, Tocopherol, 1,2-Hexanediol, Carbomer, Sodium Hydroxide, Trisodium EDTA, Dehydroacetic Acid, Phenoxyethanol</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1676,33 +1676,37 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Butylene Glycol [1,2] / 1,2-Hexanediol [1,2] / Carbomer [1,4,6] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Q10, Shea Butter</t>
+          <t>unknown — manual review needed: Ethylhexyl Cocoate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Glyceryl Stearate Citrate, Octyldodecanol, Tocopheryl Acetate, Ubiquinone, Biotin, Biosaccharide Gum-1, Sodium Ascorbyl Phosphate, Zea Mays (Corn) Oil, Beta-Carotene, Sodium Hydroxide, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>paraben or DMDM hydantoin</t>
+          <t>carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: paraben or DMDM hydantoin.</t>
+          <t>4 flagged ingredient(s) in the printed list (Butylene Glycol, 1,2-Hexanediol, Carbomer); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. Paraben/DMDM rule source: CVS 1.7 OZ (https://www.cvs.com/shop/ingredients/eucerin-sensitive-skin-experts-q10-anti-wrinkle-face-creme-1-7-oz-prodid-361289) (practitioner directive 2026-10-17). The brand's own printed text is 'Q10, Shea Butter' and does not include them; the variant match is not confirmed, so the tier rests on the retailer listing. 2 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 2 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule). Practitioner rule (2026-10-17): tier set from the retailer listing (METHYLPARABEN, ETHYLPARABEN, PROPYLPARABEN, BUTYLPARABEN, ISOBUTYLPARABEN, DMDM HYDANTOIN). The brand's printed text does not include them.</t>
+          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. Audit notes: Replaced with full brand-site list. CVS candidate formula removed: it differs (parabens, DMDM hydantoin, titanium dioxide). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full ingredients (Learn more, View all).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Urea, Cetearyl Alcohol, Hydrogenated Cocoglycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Glyceryl Stearate SE, Ceramide NP, Lactic Acid, Arginine HCI, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Dimethicone, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Cetearyl Sulfate, Sodium Chloride</t>
+          <t>Water, Glycerin, Urea, Cetearyl Alcohol, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Glyceryl Stearate SE, Ceramide NP, Lactic Acid, Arginine HCL, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Dimethicone, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Cetearyl Sulfate, Sodium Chloride</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -530,7 +530,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Urea, Hydrogenated Cocoglycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCI, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+          <t>unknown — manual review needed: Urea, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCL, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -540,12 +540,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Target product is Eucerin Advanced Repair Fragrance Free Body Cream 16oz (the 16 oz Advanced Repair Cream). First 3 ingredients match brand-site text. Full list read from the page data field nutrition_facts.ingredients (the same text the Label info section shows). Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Target (https://www.target.com/p/eucerin-advanced-repair-fragrance-free-body-cream-for-dry-skin-unscented-16oz/-/A-76525854). Ingredient-name differences: only in the full brand list: Arginine HCL; only in the previous text: Hydrogenated Cocoglycerides, Arginine HCI. Identical printed text on 1 other product(s): Advanced Repair Cream, 8 OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Cetearyl Alcohol, Glyceryl Glucosdie, Cyclomethicone, Soidum Lactate, Butyrospemum Parkii (Shea) Butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Glyceryl Stearate SE, Hydrogenated Coco-Glycerides, Arginine HCL, Sodium PCA, Dimethiconol, Lactic Acid, Chondrus Crispus (Carrageenan), Carnitine, Ceramide 3, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL, Sodium Chloride, Sodium Cetearyl Sulfate, 1,2-Hexanediol, Phenoxyethanol</t>
+          <t>Water, Glycerin, Urea, Cetearyl Alcohol, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Dimethicone, Glyceryl Stearate SE, Hydrogenated Coco-Glycerides, Carnitine, Ceramide NP, Sodium PCA, Arginine HCL, Serine, Arginine, Alanine, Histidine HCl, Citrulline, Lysine HCl, Lactic Acid, Glycogen, Mannitol, Sucrose, PCA, Glutamic acid, Threonine, Chondrus Crispus, Sodium Chloride, Sodium Cetearyl Sulfate, Tocopherol, 1,2-Hexanediol, Phenoxyethanol</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -590,13 +590,13 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cyclomethicone [1,2,6] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8]</t>
+          <t>Dimethicone [2,6] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: glyceryl glucoside, sodium lactate, butyrospermum parkii (shea) butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Arginine HCL, Sodium PCA, Dimethiconol, Lactic Acid, Chondrus Crispus (Carrageenan), Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL</t>
+          <t>unknown — manual review needed: Urea, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Caprylic/Capric Triglyceride, Methylpropanediol, Octyldodecanol, Dicaprylyl Ether, Tapioca Starch, Hydrogenated Coco-Glycerides, Carnitine, Sodium PCA, Arginine HCL, Serine, Arginine, Alanine, Histidine HCl, Citrulline, Lysine HCl, Lactic Acid, Glycogen, Mannitol, Sucrose, PCA, Glutamic acid, Threonine, Chondrus Crispus</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -606,17 +606,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Cyclomethicone, Sodium Cetearyl Sulfate, 1,2-Hexanediol); tier applies to the printed subset only. 25 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Dimethicone, Sodium Cetearyl Sulfate, 1,2-Hexanediol); tier applies to the printed subset only. 27 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 25 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2 (2026-10-16): CVS Eucerin Advanced Repair Body Lotion, 13.5 OZ pump (prodid 361273) prints a list starting Water, Glycerin, Urea, but it is a different size and pump format and does not state fragrance-free; the brand prints no size, so not used. The Walmart FF 16.9 fl oz copy (ingredients_verbatim) still conflicts with the brand text (no Urea, different first ingredients). Walgreens: blocked by a bot-check page, not attempted further. Ulta: holding page. Dermstore: no results. Amazon: not checked for this row. Unresolved. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Lotion-Fragrance-Free-16-9-fl-oz-500-ml/798125970). Ingredient-name differences: only in the full brand list: Urea, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii Butter, Dimethicone, Ceramide NP, Arginine, PCA, Tocopherol; only in the previous text: Glyceryl Glucosdie, Cyclomethicone, Soidum Lactate, Butyrospemum Parkii Butter, Dimethiconol, Ceramide 3. Candidate retailer listing removed (CVS 13.5 OZ pump, not used); its text differs from the brand list (similarity 0.76), so it is not a match. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 27 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Active Ingredients: CERAMIDE 3, NATURAL MOISTURIZING FACTORS Inactive Ingredients: Water, Glycerin, Urea, Glyceryl Stearate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Stearyl Alcohol, Dicaprylyl Ether, Cetearyl Alcohol, Sodium Lactate, Tapioca Starch, Glyceryl Stearate SE, Ceramide NP, Lactic Acid, Sodium PCA, Arginine HCI, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Dimethicone, Xanthan Gum, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Sodium Cetearyl Sulfate, Sodium Chloride.</t>
+          <t>Water, Glycerin, Urea, Glyceryl Stearate, Dibutyl Adipate, Stearyl Alcohol, Dicaprylyl Ether, Cetearyl Alcohol, Sodium Lactate, Tapioca Starch, Glyceryl Stearate SE, Ceramide NP, Lactic Acid, Sodium PCA, Arginine HCL, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Dimethicone, Xanthan Gum, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Sodium Cetearyl Sulfate</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,7 +662,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: NATURAL MOISTURIZING FACTORS, Urea, Glyceryl Stearate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Dicaprylyl Ether, Sodium Lactate, Tapioca Starch, Lactic Acid, Sodium PCA, Arginine HCI, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil</t>
+          <t>unknown — manual review needed: Urea, Glyceryl Stearate, Dibutyl Adipate, Dicaprylyl Ether, Sodium Lactate, Tapioca Starch, Lactic Acid, Sodium PCA, Arginine HCL, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: CVS listing Eucerin Advanced Repair Hand Cream, 2.7 OZ (prodid 2410039), printed Ingredients block. First 3 inactive ingredients (Water, Glycerin, Urea) match brand-site text. Walmart copy (kept in walmart_alt_text) does not list Water and starts Glycerin, Urea; the two retailer texts differ, noted here. Walmart and CVS spellings kept as printed. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: CVS (https://www.cvs.com/shop/ingredients/eucerin-advanced-repair-hand-cream-2-7-oz-prodid-2410039). Ingredient-name differences: only in the full brand list: Dibutyl Adipate, Arginine HCL; only in the previous text: CERAMIDE 3, NATURAL MOISTURIZING FACTORS, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyl Adipate, Arginine HCI, Sodium Chloride. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Advanced Repair Cleansing Body and Face Cleanser, 16.9 fl oz. First 3 ingredients match brand-site text. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Cleansing-Body-and-Face-Cleanser-16-9-Fl-Oz/810663311). Previous verbatim text was identical to the full list. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Urea, Cetearyl Alcohol, Hydrogenated Coco-Glycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Glyceryl Stearate SE, Ceramide NP, Lactic Acid, Arginine HCl, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Dimethicone, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Cetearyl Sulfate, Sodium Chloride</t>
+          <t>Water, Glycerin, Urea, Cetearyl Alcohol, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Glyceryl Stearate SE, Ceramide NP, Lactic Acid, Arginine HCL, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Dimethicone, Pentylene Glycol, Phenoxyethanol, Decylene Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Cetearyl Sulfate, Sodium Chloride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -790,7 +790,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Urea, Hydrogenated Coco-Glycerides, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCl, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
+          <t>unknown — manual review needed: Urea, Octyldodecanol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Lactate, Lactic Acid, Arginine HCL, Glycine, Alanine, Carnitine, Sodium PCA, Carrageenan, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Advanced Repair Body Cream, Fragrance Free, 8 oz tube (sold as Advanced Repair Cream 8 oz tube). First 3 match brand-site text. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Repair-Body-Cream-Fragrance-Free-8-oz-Tube/605042046). Ingredient-name differences: only in the previous text: Hydrogenated Coco-Glycerides. Identical printed text on 1 other product(s): Advanced Repair Cream, 16 OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Alcohol Denat., Cetearyl Alcohol, Diisopropyl Adipate, Panthenol, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Behenyl Alcohol, Cetyl Palmitate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Sodium Hyaluronate, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Citric Acid, Tapioca Starch, Xanthan Gum, Pantolactone, Trisodium EDTA, Ethylhexylglycerin, Caprylyl Glycol, Phenoxyethanol, Fragrance</t>
+          <t>Water, Glycerin, Alcohol Denat., Cetearyl Alcohol, Diisopropyl Adipate, Panthenol, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Behenyl Alcohol, Cetyl Palmitate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Sodium Hyaluronate, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Citric Acid, Tapioca Starch, Xanthan Gum, Pantolactone, Trisodium EDTA, Ethylhexylglycerin, Caprylyl Glycol, Phenoxyethanol, Fragrance</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -856,7 +856,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Diisopropyl Adipate, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Isobutylamido Thiazolyl Resorcinol, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Tapioca Starch, Pantolactone, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Diisopropyl Adipate, Caprylic/Capric Triglyceride, Glyceryl Stearate Citrate, Butyrospermum Parkii (Shea) Butter, Cocoglycerides, Distarch Phosphate, Lactic Acid, Glycyrrhiza Inflata Root Extract, Hydroxypropyl Starch Phosphate, Triisostearin, Sodium Hydroxide, Tapioca Starch, Pantolactone, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: CVS listing Eucerin Radiant Tone Dark Spot Corrector Body Cream, 7 OZ (prodid 922144), the only listing under this name found on CVS, Walmart or Amazon. First 3 ingredients (Water, Glycerin, Alcohol Denat.) match brand-site text. Brand site prints no size, so the 7 oz size is not confirmed by the brand. Fragrance listed without breakdown; the grader will flag it. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: CVS (https://www.cvs.com/shop/ingredients/eucerin-radiant-tone-dark-spot-corrector-body-cream-7-oz-prodid-922144). Ingredient-name differences: only in the previous text: Isobutylamido Thiazolyl Resorcinol. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Water, Alcohol Denat., Butylene Glycol, Glycerin, Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Cetearyl Alcohol, Distarch Phosphate, Sodium Hyaluronate, Tocopherol, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dimethicone, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Xanthan Gum, Gellan Gum, Sodium Chloride, Phenoxyethanol, Ethylhexylglycerin, Trisodium EDTA, Citric Acid, Fragrance.</t>
+          <t>Water, Alcohol Denat., Butylene Glycol, Glycerin, Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Cetearyl Alcohol, Distarch Phosphate, Sodium Ascorbyl Phosphate, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Tocopherol, Glucosylrutin, Sodium Stearoyl Glutamate, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Xanthan Gum, Gellan Gum, Dimethicone, Isoquercitrin, Citric Acid, Sodium Chloride, Ethylhexylglycerin, Trisodium EDTA, Phenoxyethanol</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -912,17 +912,17 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat) / Butylene Glycol [1,2] / Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Butylene Glycol [1,2] / Dimethicone [2,6] / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Isoquercitrin, Glycine Soja (Soybean) Oil, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Sodium Stearoyl Glutamate, Gellan Gum, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Sodium Stearoyl Glutamate, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Gellan Gum, Isoquercitrin, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, Dimethicone); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, Dimethicone); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648). Ingredient-name differences: only in the previous text: Isobutylamido Thiazolyl Resorcinol, Glycine Soja Oil, Fragrance. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Caprylic/Capric Triglyceride, Alcohol Denat., Cocoglycerides, Cetearyl Alcohol, Isopropyl Palmitate, Cetyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Lauroyl Lysine, SodiumHyaluronate, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Synthetic Fluorphlogopite, SodiumStearoyl Glutamate, Citric Acid, Xanthan Gum, Phenoxyethanol, Ethylhexylglycerin, SodiumHydroxide, Trisodium EDTA, Titanium Dioxide, Tin Oxide, Iron Oxides.</t>
+          <t>Water, Glycerin, Caprylic/Capric Triglyceride, Alcohol Denat., Cocoglycerides, Cetearyl Alcohol, Cetyl Palmitate, Isopropyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Lauroyl Lysine, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Xanthan Gum, Sodium Stearoyl Glutamate, Sodium Chloride, Citric Acid, Sodium Hydroxide, Phenoxyethanol, Ethylhexylglycerin, Synthetic Fluorphlogopite, Trisodium EDTA, Tin Oxide, Titanium Dioxide, Iron Oxides, Iron Oxides</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -982,13 +982,13 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat) / Synthetic Fluorphlogopite [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Iron Oxides [1,2,3]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5] / Synthetic Fluorphlogopite [1,2] / Iron Oxides [1,2,3]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Cocoglycerides, Isopropyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Isobutylamido Thiazolyl Resorcinol, Sodium Stearoyl Glutamate, Sodium Hydroxide, Trisodium EDTA, Tin Oxide</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Cocoglycerides, Isopropyl Palmitate, Glyceryl Stearate, Diisopropyl Adipate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Pimpinella Anisum (Anise) Fruit Extract, Sodium Stearoyl Glutamate, Sodium Hydroxide, Trisodium EDTA, Tin Oxide</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Synthetic Fluorphlogopite, Phenoxyethanol); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Ethylhexylglycerin); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from flags (2026-10-17). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Radiant Tone Eye Cream, Dark Circle Corrector, 0.5 oz. First 3 match brand-site text. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DRK-EYE-CRM-0-5-OZ/18839271130). Ingredient-name differences: only in the full brand list: Sodium Chloride; only in the previous text: Isobutylamido Thiazolyl Resorcinol. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Alcohol Denat., Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Ceteary Alcohol, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Isobutylamido Thiazolyl Resorcinol, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Xanthan Gum, Sodium Stearoyl Glutamate, Ethylhexylglycerin, Phenoxyethanol, Trisodium EDTA, Citric Acid, Fragrance</t>
+          <t>Water, Glycerin, Alcohol Denat., Diisopropyl Adipate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Cetearyl Alcohol, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Xanthan Gum, Sodium Stearoyl Glutamate, Ethylhexylglycerin, Phenoxyethanol, Trisodium EDTA, Citric Acid, Fragrance</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1054,7 +1054,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Diisopropyl Adipate, Butylene Glycol Dicaprylate/ Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Sodium Stearoyl Glutamate, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Diisopropyl Adipate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Distarch Phosphate, Glyceryl Stearate, Glycyrrhiza Inflata Root Extract, Tocopheryl Acetate, Sodium Stearoyl Glutamate, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Alcohol Denat, Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Radiant Tone Dark Spot Corrector Body Lotion, 8.4 fl oz. First 3 match brand-site text. Retailer text includes Fragrance (no breakdown), which the grader will flag. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/EUC-RDN-TN-BDY-LTN-8-4OZ/20570517080). Ingredient-name differences: only in the full brand list: Cetearyl Alcohol; only in the previous text: Ceteary Alcohol, Isobutylamido Thiazolyl Resorcinol. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1101,7 +1101,8 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Active: Avobenzone 3% , Homosalate 8%, Octisalate 4.5%, Octocrylene 9%. Inactive: Water, Glycerin, Alcohol Denat., Glyceryl Stearate, Silica, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Cetearyl Alcohol, Dibutyl Adipate, Silica Dimethyl Silylate, Tocopherol, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Xanthan Gum, Phenoxyethanol, Ethylhexylglycerin, Disodium EDTA, Sodium Chloride, Fragrance.</t>
+          <t>Active Ingredients: Avobenzone (3%), Homosalate (8%), Octisalate (4.5%), Octocrylene (9%)
+Inactive Ingredients: Water, Glycerin, Alcohol Denat., Glyceryl Stearate, Silica, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Cetearyl Alcohol, Dibutyl Adipate, Silica Dimethyl Silylate, Tocopherol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Xanthan Gum, Phenoxyethanol, Ethylhexylglycerin, Disodium EDTA, Sodium Chloride, Fragrance</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1120,7 +1121,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glyceryl Stearate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Isobutylamido Thiazolyl Resorcinol, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA</t>
+          <t>unknown — manual review needed: Glyceryl Stearate, Butylene Glycol Dicaprylate/Dicaprate, C12-15 Alkyl Benzoate, Dibutyl Adipate, Silica Dimethyl Silylate, Glycyrrhiza Inflata Root Extract, Sodium Stearoyl Glutamate, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1130,12 +1131,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>9 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
+          <t>9 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Radiant Tone Daily Face Lotion SPF 30, 1.7 fl oz. Active percentages match brand-site text. Walmart prints Active:/Inactive: labels, kept as printed. Fragrance listed without breakdown. Brand site printed the active list only; this is a face lotion listing matched to the brand Daily Lotion SPF 30 by active percentages. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Daily-SPF-Lotion/13188257095). Ingredient-name differences: only in the previous text: Isobutylamido Thiazolyl Resorcinol. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1167,7 +1168,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Alcohol Denat., Butyrospermum Parkii (Shea) Butter, Squalane, Cetearyl Isononanoate, Panthenol, Isopropyl Palmitate, Glyceryl Stearate Citrate, Cetearyl Alcohol, Hydrogenated Coco-Glycerides, Methylpropanediol, Lauroyl Lysine, Tocopherol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate, Xanthan Gum, Phenoxyethanol, Trisodium Ethylenediamine Disuccinate, Citric Acid, Fragrance.</t>
+          <t>Water, Glycerin, Alcohol Denat., Butyrospermum Parkii (Shea) Butter, Cetearyl Isononanoate, Panthenol, Glyceryl Stearate Citrate, Cetearyl Alcohol, Lauroyl Lysine, Glycyrrhiza Inflata Root Extract, Tocopherol, Glucosylrutin, Pantolactone, Xanthan Gum, Isoquercitrin, Distarch Phosphate, Citric Acid, Trisodium Ethylenediamine Disuccinate, Phenoxyethanol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1176,17 +1177,17 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat) / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Phenoxyethanol [1,2,4,5,8]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter, Cetearyl Isononanoate, Isopropyl Palmitate, Glyceryl Stearate Citrate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Glucosylrutin, Pantolactone, Glycyrrhiza Inflata Root Extract, Isoquercitrin, Distarch Phosphate</t>
+          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter, Cetearyl Isononanoate, Glyceryl Stearate Citrate, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Pantolactone, Isoquercitrin, Distarch Phosphate</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1196,12 +1197,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol, Fragrance); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Alcohol Denat, Phenoxyethanol); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Radiant Tone Night Cream, Dark Spot Corrector, 1.7 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Radiant-Tone-Dark-Spot-Corrector-Night-Cream/13168604313). Ingredient-name differences: only in the previous text: Squalane, Isopropyl Palmitate, Hydrogenated Coco-Glycerides, Methylpropanediol, Isobutylamido Thiazolyl Resorcinol, Fragrance. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1233,7 +1234,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Water, Alcohol Denat., Sodium Cocoamphoacetate, Glycerin, Coco-Betaine, Lactic Acid, SodiumChloride, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside, Sodium Hydroxide, SodiumBenzoate.</t>
+          <t>Water, Alcohol Denat., Sodium Cocoamphoacetate, Glycerin, Coco-Betaine, Lactic Acid, Sodium Chloride, Dehydroxanthan Gum, Glycolic Acid, Glyceryl Glucoside, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1263,7 +1264,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Radiant Tone Face Cleanser Gel with 2% AHA Complex, 6.8 fl oz. First 3 match brand-site text. Walmart spellings (SodiumChloride, Dehydroxanthan Gum) kept as printed. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-CLNSG-GEL-6-8-FLOZ/13165700363). Ingredient-name differences: only in the previous text: SodiumBenzoate. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1329,7 +1330,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Amazon listing Eucerin Immersive Hydration Replenishing Night Gel Face Cream, 1.7 oz. The page Q&amp;A and shop list name this product Immersive Hydration Gel-Cream, which matches the brand product. First 3 match brand-site text (Water, Alcohol Denat., Glycerin). Same list as Walmart 7814860905 (earlier candidate). Fragrance listed without breakdown. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Amazon (https://www.amazon.com/dp/B0CHD4M1FT). Previous verbatim text was identical to the full list. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1395,7 +1396,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 1 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Immersive Hydration Smoothing Face Serum with Hyaluronic Acid, 1 fl oz (Moisture Boost line). First 3 match brand-site text. Fragrance listed without breakdown. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Immersive-Hydration-Moisture-Boost-Face-Serum-Ultra-Lightweight-Hyaluronic-Acid-Serum-Smooths-Fine-Lines-and-Wrinkles-1-Fl-Oz-Bottle/10283316616). Previous verbatim text was identical to the full list. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 1 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1427,7 +1428,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hyaluronate, Trisodium EDTA, Sodium Chloride, Sodium Benzoate</t>
+          <t>Water, Glycerin, Coco-Betaine, Coco-Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hyaluronate, Sodium Chloride, Trisodium EDTA, Sodium Benzoate</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1442,18 +1443,18 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Coco-Betaine, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 5 unknown ingredient(s) not in reference, excluded from grade.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 4 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 6.8 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Face Hydrating Cleansing Gel Facial Cleanser with Hyaluronic Acid, 13.5 fl oz. First 3 match brand-site text. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Face-Gentle-Cleansing-Hydrating-Cleansing-Gel-Daily-Face-Wash-and-Makeup-Remover-with-Hyaluronic-Acid-13-5-Fl-Oz-Bottle/5161786479). Same ingredient names as the previous text; wording, spelling or order differs. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1485,7 +1486,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hyaluronate, Trisodium EDTA, Sodium Chloride, Sodium Benzoate</t>
+          <t>Water, Glycerin, Coco-Betaine, Coco-Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hyaluronate, Trisodium EDTA, Sodium Chloride, Sodium Benzoate</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1500,18 +1501,18 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Coco-Betaine, Coco Glucoside, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Coco-Betaine, Glyceryl Glucoside, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 5 unknown ingredient(s) not in reference, excluded from grade.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 4 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Identical printed text on 1 other product(s): Hydrating Cleansing Gel, 13.5 FL OZ. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Amazon (https://www.amazon.com/dp/B094NWLKKZ).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Amazon listing Eucerin Hydrating Cleansing Gel with Hyaluronic Acid, 6.8 fl oz (size matches brand title). Brand text is key ingredients only (Hyaluronic acid, Gluco-Glycerol, APG Complex); all three appear in this list (Sodium Hyaluronate, Glyceryl Glucoside, Coco Glucoside). Brand printed no INCI start, so the first-ingredient cross-check is limited. Walmart 13.5 fl oz listing (same formula) is product 15. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Amazon (https://www.amazon.com/dp/B094NWLKKZ). Same ingredient names as the previous text; wording, spelling or order differs. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1543,7 +1544,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Water, Mineral Oil, Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Glycerin, PEG-7 Hydrogenated Castor Oil, Benzyl Alcohol, Dimethicone, Methoxy PEG-22/Dodecyl Glycol Copolymer, PEG-45/Dodecyl Glycol Copolymer, Magnesium Sulfate, Lactic Acid, Ozokerite, PEG-2 Hydrogenated Castor Oil, Sorbitan Isostearate, Hydrogenated Castor Oil.</t>
+          <t>Water, Mineral Oil, Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Glycerin, PEG-7 Hydrogenated Castor Oil, Benzyl Alcohol, Dimethicone, Methoxy PEG-22/Dodecyl Glycol Copolymer, PEG-45 Dodecyl Glycol Copolymer, Magnesium Sulfate, Lactic Acid, Microcrystalline Wax, PEG-2 Hydrogenated Castor Oil, Sorbitan Isostearate, Hydrogenated Castor Oil</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1556,13 +1557,13 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / PEG-7 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-) / Dimethicone [2,6] / PEG-45/Dodecyl Glycol Copolymer [1,2,4,5] (inferred: PEG-) / PEG-2 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-)</t>
+          <t>Mineral Oil [1] / PEG-7 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-) / Dimethicone [2,6] / PEG-45 Dodecyl Glycol Copolymer [1,2,4,5] (inferred: PEG-) / PEG-2 Hydrogenated Castor Oil [1,2,4,5] (inferred: PEG-)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Methoxy PEG-22/Dodecyl Glycol Copolymer, Lactic Acid, Ozokerite, Sorbitan Isostearate, Hydrogenated Castor Oil</t>
+          <t>unknown — manual review needed: Octyldodecanol, Caprylic/Capric Triglyceride, Isopropyl Palmitate, Sodium Lactate, Urea, Methoxy PEG-22/Dodecyl Glycol Copolymer, Lactic Acid, Microcrystalline Wax, Sorbitan Isostearate, Hydrogenated Castor Oil</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1577,12 +1578,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2: CVS Eucerin Intensive Repair Very Dry Skin Lotion, 8.4 OZ (prodid 1016683) prints a list whose first 3 ingredients match the brand text (Water, Mineral Oil, Octyldodecanol). It is the same list as the Walmart 16.9 fl oz pump already in ingredients_verbatim. CVS shows this name in 2 sizes and the brand site prints no size, so the size is not confirmed; held at needs review. Walgreens blocked (bot-check page). Ulta holding page. Dermstore not checked for this row. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Intensive-Repair-Body-Lotion-Fragrance-Free-Body-Moisturizer-16-9-fl-oz-Bottle/10413395). Ingredient-name differences: only in the full brand list: Microcrystalline Wax; only in the previous text: Ozokerite. Candidate retailer listing kept (CVS 8.4 OZ, same product page family); its text agrees with the brand list (similarity about 0.96), with naming differences only. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1609,38 +1610,46 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Water, Glycerin, Ethylhexyl Cocoate, Hydrogenated Coco-Glycerides, Stearyl Alcohol, Butylene Glycol, Cetyl Alcohol, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Glyceryl Stearate Citrate, Octyldodecanol, Macadamia Ternifolia Seed Oil, Ubiquinone, Retinyl Palmitate, Carbomer, Trisodium EDTA, 1,2-Hexanediol, Dehydroacetic Acid</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Butylene Glycol [1,2] / Carbomer [1,4,6] / 1,2-Hexanediol [1,2]</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Q10</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>unknown — manual review needed: Ethylhexyl Cocoate, Hydrogenated Coco-Glycerides, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Glyceryl Stearate Citrate, Octyldodecanol, Macadamia Ternifolia Seed Oil, Ubiquinone, Retinyl Palmitate, Trisodium EDTA</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ungradable: source text unresolved (practitioner exception, 2026-10-17). Partial flags recorded: 0.</t>
+          <t>3 flagged ingredient(s) in the printed list (Butylene Glycol, Carbomer, 1,2-Hexanediol); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. 1 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 1 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Q10.</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2: No Q10 Revitalize Night Cream found. CVS brand shop and search did not return it. Amazon search returned no Eucerin Q10 night cream (only Anti-Pigment Night Cream, a different product). Dermstore search for eucerin q10 returned no results. Walgreens blocked (bot-check page). Ulta holding page. Earlier Walmart candidate 233160412 contains Retinyl Palmitate (different formula, not used). Unresolved. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: none recorded (key ingredients only). Ingredient-name differences: only in the full brand list: Water, Glycerin, Ethylhexyl Cocoate, Hydrogenated Coco-Glycerides, Stearyl Alcohol, Butylene Glycol, Cetyl Alcohol, Caprylic/Capric Triglyceride, Butyrospermum Parkii Butter, Glyceryl Stearate Citrate, Octyldodecanol, Macadamia Ternifolia Seed Oil, Ubiquinone, Retinyl Palmitate, Carbomer, Trisodium EDTA, 1, 2-Hexanediol, Dehydroacetic Acid; only in the previous text: Q10. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1710,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. Audit notes: Replaced with full brand-site list. CVS candidate formula removed: it differs (parabens, DMDM hydantoin, titanium dioxide). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full ingredients (Learn more, View all).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Sensitive Skin Experts Q10 Anti-Wrinkle Face Creme 1.7 OZ (prodid 361289) prints a full list with Q10 as the active and shea butter as an inactive, and the name matches the brand URL slug. The brand prints only two key ingredients (Q10, Shea Butter), so the first-ingredient cross-check cannot be done and the variant is not clearly confirmed. Walmart Eucerin Q10 Anti-Wrinkle Face Cream 1.7 oz is also candidate only. Unresolved. The CVS text includes parabens and DMDM hydantoin. Audit notes: Replaced with full brand-site list. CVS candidate formula removed: it differs (parabens, DMDM hydantoin, titanium dioxide). Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Eucerin brand site, full ingredients (Learn more, View all). Previous verbatim text was identical to the full list. Verbatim text unchanged by the merge; ingredient_source now uses the standard brand-site label. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1733,38 +1742,46 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glycyrrhetinic Acid, Licochalcone A</t>
+          <t>Water, Alcohol Denat., Glycerin, Panthenol, Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Glyceryl Stearate SE, Butyrospermum Parkii (Shea) Butter, Cetyl Alcohol, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Tocopherol, Pantolactone, Tapioca Starch, Glycine Soja (Soybean) Oil, Dimethicone, Sodium Cetearyl Sulfate, Phenoxyethanol, Carbomer, Sodium Hydroxide, Citric Acid, Fragrance</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Dimethicone [2,6] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glycyrrhetinic Acid, Licochalcone A</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>unknown — manual review needed: Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Pantolactone, Tapioca Starch, Glycine Soja (Soybean) Oil, Sodium Hydroxide</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 2 unknown ingredient(s) not in reference, excluded from grade.</t>
+          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Dimethicone, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row. 2 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 2 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2: CONFLICT, not used. CVS Eucerin Advanced Hydration After Sun Lotion, 6.8 OZ (prodid 145120) lists Glycyrrhetinic Acid but not Licochalcone A, which the brand lists as a key ingredient. The CVS list also includes Fragrance. Walmart After Sun Moisturizing Lotion 6.7 fl oz conflicts too (no Licochalcone A). Held at needs review with both texts kept. Walgreens blocked. Ulta holding page. Dermstore not checked for this row. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: none recorded (key ingredients only). Ingredient-name differences: only in the full brand list: Water, Alcohol Denat, Glycerin, Panthenol, Hydrogenated Coco-Glycerides, Isopropyl Palmitate, Glyceryl Stearate SE, Butyrospermum Parkii Butter, Cetyl Alcohol, Glycyrrhiza Inflata Root Extract, Tocopherol, Pantolactone, Tapioca Starch, Glycine Soja Oil, Dimethicone, Sodium Cetearyl Sulfate, Phenoxyethanol, Carbomer, Sodium Hydroxide, Citric Acid, Fragrance; only in the previous text: Licochalcone A. Candidate retailer listing removed (CVS 6.8 OZ); its text differs from the brand list (similarity 0.66), so it is not a match. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1842,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Sensitive Mineral SPF 50 Sunscreen Lotion. 8 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand site prints actives only, so the inactive list cannot be cross-checked. Size not printed on brand listing. Walmart prints Active/Inactive labels; kept verbatim. Audit notes: Retailer fallback 2026-10-17. Brand site shows Active Ingredients only, no full list. CVS: search found an Eucerin Sun Sensitive Mineral SPF 50 4 oz listing, but its product page returned Access Denied. Walgreens: bot-challenge page, not completed. Target: no Sensitive Mineral SPF 50 listing. Walmart: 'Eucerin Sun Sensitive Mineral Sunscreen Lotion SPF 50, 4 Fl Oz Tube'; Ingredients block copied verbatim (Active Zinc Oxide 24% matches the brand key ingredient). Needs review: the brand page prints no size, and Walmart also lists a near-identical 'With Zinc Oxide Protection, 4 Fl Oz Tube' variant, so size and variant are not confirmed. 8 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sensitive-Mineral-Broad-Spectrum-Lightweight-Sunscreen-Lotion-SPF-50-4-fl-oz/904251650).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1908,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Amazon listing Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 fl oz (Ultra-Light). Active percentages match brand-site text. Walmart and Ulta/Target not usable for this product. Note: the Amazon page text shows the inactive ingredient as l-6 Stearate, apparently a clipped Polyglyceryl-6 Stearate; kept as printed in the page text, verify before publishing. Audit notes: Retailer fallback 2026-10-17. Brand site shows Active Ingredients only, no full list. CVS: product pages returned Access Denied (see product 20); not searched for this product. Walgreens: bot-challenge page, not completed. Target: no match. Walmart: no listing with the 'Advanced Hydration Ultra-Light Face Sunscreen' name in search results. Amazon: 'Eucerin Advanced Hydration Face Sunscreen Lotion, SPF 50, 1.7 FL OZ | Ultra-Light Fluid'; Ingredients block copied verbatim (actives match the brand key ingredients). Needs review: the brand page prints no size, and the Amazon title reads 'Face Sunscreen Lotion' rather than the brand's name, so size and name are not confirmed. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Amazon (https://www.amazon.com/dp/B0DJTXV6XQ).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1974,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray, 6 oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Spray format: propellant Dimethyl Ether listed. Audit notes: Retailer fallback 2026-10-17. Brand site shows Active Ingredients only, no full list. CVS: product pages returned Access Denied (see product 20); not searched for this product. Walgreens: bot-challenge page, not completed. Target: not checked for this product. Walmart: 'Eucerin Sun Advanced Hydration SPF 50 Sunscreen Spray with Hyaluronic Acid, Hydrates Skin, 6 oz'; Ingredients block copied verbatim (actives match the brand key ingredients). The same page shows a stray 'Active Ingredients: salicylic acid' block that is not part of this product's printed list and was not used. Needs review: the brand page prints no size, so size is not confirmed. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Advanced-Hydration-Sunscreen-Spray-SPF-50-6-fl-oz-Bottle/131984769).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1989,7 +2006,8 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Active Ingredients: Avobenzone 3%, Homosalate 9%, Octisalate 4.5%, Octocrylene 9%... Inactive Ingredients: Water, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Styrene/Acrylates Copolymer, Butylene Glycol, Diethylhexyl Syringylidenemalonate, VP/Eicosene Copolymer, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Tocopherol, Aloe Barbadensis Leaf Juice, 1,2-Hexandiol, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Potassium Hydroxide, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
+          <t>Active Ingredients: Avobenzone (3%), Homosalate (9%), Octisalate (4.5%), Octocrylene (9%)
+Inactive Ingredients: Water, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Styrene/Acrylates Copolymer, Butylene Glycol, Diethylhexyl Syringylidenemalonate, VP/Eicosene Copolymer, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Tocopherol, Aloe Barbadensis Leaf Juice, 1,2-Hexanediol, Hydroxyacetophenone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Potassium Hydroxide, Disodium EDTA, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2002,7 +2020,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Styrene/Acrylates Copolymer [1,4,6] / Butylene Glycol [1,2] / Diethylhexyl Syringylidenemalonate [2] / VP/Eicosene Copolymer [1,2,6] / 1,2-Hexandiol [1,2] / Potassium Hydroxide [4]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Styrene/Acrylates Copolymer [1,4,6] / Butylene Glycol [1,2] / Diethylhexyl Syringylidenemalonate [2] / VP/Eicosene Copolymer [1,2,6] / 1,2-Hexanediol [1,2] / Potassium Hydroxide [4]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2023,7 +2041,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Sun Advanced Hydration SPF 50 Sunscreen Lotion with Hyaluronic Acid, 5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Advanced-Hydration-Lightweight-Sunscreen-Lotion-Adult-SPF-50-5-fl-oz/596634962). Ingredient-name differences: only in the full brand list: 2-Hexanediol; only in the previous text: 2-Hexandiol. 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2055,7 +2073,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Active Ingredients: Zinc Oxide 24%... Inactive Ingredients: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Butyloctyl Salicylate, Ethylhexyl Pelargonate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol, Cyclopentasiloxane, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Dimethicone, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Beeswax, Hydroxyacetophenone, Sodium Chloride, PEG-12 Dimethicone Crosspolymer, 1,2-Hexanediol, Caprylyl Glycol, Tocopherol</t>
+          <t>Active Ingredients: Zinc Oxide (24%) Inactive Ingredients: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Butyloctyl Salicylate, Ethylhexyl Pelargonate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol, Cyclopentasiloxane, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Dimethicone, Ethylhexyl Methoxycrylene, Polyester-27, Triethoxycaprylylsilane, Beeswax, Hydroxyacetophenone, Sodium Chloride, PEG-12 Dimethicone, 1,2-Hexanediol, Caprylyl Glycol, Tocopherol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2068,7 +2086,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Butyloctyl Salicylate [2] / Cetyl PEG/PPG-10/1 Dimethicone [2,6] (inferred: silicone) / Propylene Glycol [1,2] / Cyclopentasiloxane [1,2,6] / Dimethicone [2,6] / PEG-12 Dimethicone Crosspolymer [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2]</t>
+          <t>Butyloctyl Salicylate [2] / Cetyl PEG/PPG-10/1 Dimethicone [2,6] (inferred: silicone) / Propylene Glycol [1,2] / Cyclopentasiloxane [1,2,6] / Dimethicone [2,6] / PEG-12 Dimethicone [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -2089,7 +2107,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Identical printed text on 1 other product(s): Sensitive Mineral SPF 50 Sunscreen. 8 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Baby Sunscreen SPF 50, 4 fl oz tube. Zinc Oxide 24% matches brand-site text. Brand prints actives only. Walmart text kept verbatim with its Active/Inactive labels. Size not printed on brand listing. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Sensitive-Mineral-Baby-Sunscreen-SPF-50-4-Fl-Oz-Tube/485084849). Ingredient-name differences: only in the full brand list: PEG-12 Dimethicone; only in the previous text: PEG-12 Dimethicone Crosspolymer. 8 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2121,7 +2139,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Active: Avobenzone 3%, Homosalate 10%, Octisalate 5%, Octocrylene 10%... Inactive: Water, Alcohol Denat., Butyloctyl Salicylate, Silica, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Behenyl Alcohol, Butylene Glycol Dicaprylate/Dicaprate, Cetearyl Alcohol, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Tocopherol, Dimethicone, Silica Dimethyl Silylate, Diethylhexyl Syringylidenemalonate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Phenoxyethanol, Glycerin, Xanthan Gum, Ethylhexylglycerin, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Cetyl Alcohol, Sodium Ascorbyl Phosphate</t>
+          <t>Active Ingredients: Avobenzone (3%), Homosalate (10%), Octisalate (5%), Octocrylene (10%) Inactive Ingredients: Water, Alcohol Denat., Butyloctyl Salicylate, Silica, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Behenyl Alcohol, Butylene Glycol Dicaprylate/Dicaprate, Cetearyl Alcohol, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Tocopherol, Dimethicone, Silica Dimethyl Silylate, Diethylhexyl Syringylidenemalonate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Phenoxyethanol, Glycerin, Xanthan Gum, Ethylhexylglycerin, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Cetyl Alcohol, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2140,7 +2158,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, L-Carnitine, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Butylene Glycol Dicaprylate/Dicaprate, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, L-Carnitine, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2155,7 +2173,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 18 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Sun Clear Skin Face Sunscreen, SPF 50, Oily Skin, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/ESUN-OIL-CNT-FC-LTN-SPF50-2-5FLOZ/900570371). Same ingredient names as the previous text; wording, spelling or order differs. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 18 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2187,7 +2205,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Active Ingredients: Avobenzone 3%, Homosalate 10%, Octisalate 5%, Octocrylene 10%... Inactive Ingredients: Water, Alcohol Denat., Butyloctyl Salicylate, Silica, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Behenyl Alcohol, Butylene Glycol Dicaprylate/Dicaprate, Cetearyl Alcohol, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Tocopherol, Dimethicone, Silica Dimethyl Silylate, Diethylhexyl Syringylidenemalonate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Phenoxyethanol, Glycerin, Xanthan Gum, Ethylhexylglycerin, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Cetyl Alcohol, Sodium Ascorbyl Phosphate</t>
+          <t>Active Ingredients: Avobenzone (3%), Homosalate (10%), Octisalate (5%), Octocrylene (10%) Inactive Ingredients: Water, Alcohol Denat., Butyloctyl Salicylate, Silica, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Behenyl Alcohol, Butylene Glycol Dicaprylate/Dicaprate, Cetearyl Alcohol, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Tocopherol, Dimethicone, Silica Dimethyl Silylate, Diethylhexyl Syringylidenemalonate, Ethylcellulose, Glyceryl Behenate, L-Carnitine, Polyglyceryl-6 Octastearate, Phenoxyethanol, Glycerin, Xanthan Gum, Ethylhexylglycerin, Disodium EDTA, Hydroxyacetophenone, Polyglyceryl-6 Behenate, Cetyl Alcohol, Sodium Ascorbyl Phosphate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2221,7 +2239,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 18 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Sun Age Defense Face Sunscreen Lotion, SPF 50, 2.5 fl oz. Active percentages match brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/ESUN-AGE-DFN-FC-LTN/170994848). Same ingredient names as the previous text; wording, spelling or order differs. D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 18 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2253,7 +2271,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Active: Zinc Oxide 24% Inactive: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Butyloctyl Salicylate, Ethylhexyl Pelargonate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol, Cyclopentasiloxane, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Dimethicone, Diethylhexyl Syringylidenemalonate, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Tocopherol (Vitamin E), Triethoxycaprylylsilane, Beeswax, Hydroxyacetophenone, Sodium Chloride, PEG-12 Dimethicone Crosspolymer, 1,2-Hexanediol, Caprylyl Glycol, Jojoba Esters, Silica, Polyglyceryl-6 Polyricinoleate, Iron Oxides</t>
+          <t>Active Ingredients: Zinc Oxide (24%) Inactive Ingredients: Water, C12-15 Alkyl Benzoate, Isopropyl Palmitate, Butyloctyl Salicylate, Ethylhexyl Pelargonate, Cetyl PEG/PPG-10/1 Dimethicone, Propylene Glycol, Cyclopentasiloxane, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Dimethicone, Diethylhexyl Syringylidenemalonate, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis Seed Oil, Tocopherol, Triethoxycaprylylsilane, Beeswax, Hydroxyacetophenone, Sodium Chloride, PEG-12 Dimethicone, 1,2-Hexanediol, Caprylyl Glycol, Jojoba Esters, Silica, Polyglyceryl-6 Polyricinoleate, Iron Oxides</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2266,13 +2284,13 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Butyloctyl Salicylate [2] / Cetyl PEG/PPG-10/1 Dimethicone [2,6] (inferred: silicone) / Propylene Glycol [1,2] / Cyclopentasiloxane [1,2,6] / Dimethicone [2,6] / Diethylhexyl Syringylidenemalonate [2] / PEG-12 Dimethicone Crosspolymer [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Silica [1,2] / Iron Oxides [1,2,3]</t>
+          <t>Butyloctyl Salicylate [2] / Cetyl PEG/PPG-10/1 Dimethicone [2,6] (inferred: silicone) / Propylene Glycol [1,2] / Cyclopentasiloxane [1,2,6] / Dimethicone [2,6] / Diethylhexyl Syringylidenemalonate [2] / PEG-12 Dimethicone [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Silica [1,2] / Iron Oxides [1,2,3]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis (Jojoba) Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate</t>
+          <t>unknown — manual review needed: C12-15 Alkyl Benzoate, Isopropyl Palmitate, Ethylhexyl Pelargonate, Bis-Octyldodecyl Dimer Dilinoleate/Propanediol Copolymer, Ethylhexyl Methoxycrylene, Polyester-27, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Ascorbyl Phosphate, Simmondsia Chinensis Seed Oil, Triethoxycaprylylsilane, Hydroxyacetophenone, Jojoba Esters, Polyglyceryl-6 Polyricinoleate</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2287,7 +2305,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 14 unknown ingredient(s) excluded from flags (2026-10-17). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Sun Sensitive Mineral Tinted Face Sunscreen SPF 35, 1.7 fl oz. Zinc Oxide 24% matches brand-site text. Brand site lists SPF 35; Walmart title matches. Walmart prints Active/Inactive labels; kept verbatim. Iron Oxides listed without CI number. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/ESUN-TNT-MNL-FC-35/1827512195). Ingredient-name differences: only in the full brand list: PEG-12 Dimethicone; only in the previous text: PEG-12 Dimethicone Crosspolymer. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 14 unknown ingredient(s) excluded from flags (2026-10-17). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2319,7 +2337,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Active ingredients: Avobenzone 3%, Homosalate 10%, Octisalate 5%, Octocrylene 10% Inactive ingredients: Water, Alcohol Denat., Butyloctyl Salicylate, Silica, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Behenyl Alcohol, Butylene Glycol Dicaprylate/Dicaprate, Cetearyl Alcohol, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Hyaluronate, L-Carnitine, Sodium Ascorbyl Phosphate, Tocopherol (Vitamin E), Hydroxyacetophenone, Diethylhexyl Syringylidenemalonate, Dimethicone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Glycerin, Phenoxyethanol, Xanthan Gum, Ethylhexylglycerin, Polyglyceryl-6 Behenate, Cetyl Alcohol, Cellulose Gum, 1,2-Hexanediol, Caprylyl Glycol, Sodium Polyacrylate, Disodium EDTA, Iron Oxides</t>
+          <t>Active Ingredients: Avobenzone (3%), Homosalate (10%), Octisalate (5%), Octocrylene (10%) Inactive Ingredients: Water, Alcohol Denat., Butyloctyl Salicylate, Silica, C12-15 Alkyl Benzoate, Polyglyceryl-6 Stearate, Sodium Stearoyl Glutamate, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Behenyl Alcohol, Butylene Glycol Dicaprylate/Dicaprate, Cetearyl Alcohol, Copernicia Cerifera (Carnauba) Wax, Dibutyl Adipate, Glycyrrhiza Inflata Root Extract, Glycyrrhetinic Acid, Sodium Hyaluronate, L-Carnitine, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Diethylhexyl Syringylidenemalonate, Dimethicone, Silica Dimethyl Silylate, Ethylcellulose, Glyceryl Behenate, Polyglyceryl-6 Octastearate, Glycerin, Phenoxyethanol, Xanthan Gum, Ethylhexylglycerin, Polyglyceryl-6 Behenate, Cetyl Alcohol, Cellulose Gum, 1,2-Hexanediol, Caprylyl Glycol, Sodium Polyacrylate, Disodium EDTA, Iron Oxides</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2353,7 +2371,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 19 unknown ingredient(s) excluded from flags (2026-10-17). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Sun Age Defense Tinted Face Sunscreen Lotion SPF 50, 2.5 fl oz. Active percentages match brand-site text. Iron Oxides listed without CI number. Walmart label punctuation normalized in this copy only. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Sun-Tinted-Age-Defense-Face-Sunscreen-Lotion-Adult-SPF-50-2-5-fl-oz/5261126307). Ingredient-name differences: only in the previous text: Tocopherol. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 19 unknown ingredient(s) excluded from flags (2026-10-17). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written. Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2385,38 +2403,46 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Avobenzone (3%), Homosalate (7%), Octisalate (4.5%), Octocrylene (8%)</t>
+          <t>Active Ingredients: Avobenzone (3%), Homosalate (7%), Octisalate (4.5%), Octocrylene (8%) Inactive Ingredients: Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Butylene Glycol, Styrene/Acrylates Copolymer, Diethylhexyl Syringylidenemalonate, VP/Eicosene Copolymer, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Hyaluronate, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Aloe Barbadensis Leaf Juice, 1,2-Hexanediol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Butylene Glycol [1,2] / Styrene/Acrylates Copolymer [1,4,6] / Diethylhexyl Syringylidenemalonate [2] / VP/Eicosene Copolymer [1,2,6] / 1,2-Hexanediol [1,2]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Aloe Barbadensis Leaf Juice, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only.</t>
+          <t>9 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No Eucerin Advanced Hydration SPF 30 spray found. The CVS brand shop lists only Sun Advanced Hydration SPF 50 Spray 6 oz (prodid 621595). Dermstore search for eucerin sunscreen spray spf 30 returned no Eucerin SPF 30 spray. Walmart and Amazon: no listing in round 1. Walgreens blocked; Ulta holding page. Unresolved.</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2: No Eucerin Advanced Hydration SPF 30 spray found. The CVS brand shop lists only Sun Advanced Hydration SPF 50 Spray 6 oz (prodid 621595). Dermstore search for eucerin sunscreen spray spf 30 returned no Eucerin SPF 30 spray. Walmart and Amazon: no listing in round 1. Walgreens blocked; Ulta holding page. Unresolved. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: none recorded (key ingredients only). Ingredient-name differences: only in the full brand list: Dimethyl Ether, C12-15 Alkyl Benzoate, Neopentyl Glycol Diheptanoate, Butylene Glycol, Styrene/Acrylates Copolymer, Diethylhexyl Syringylidenemalonate, VP/Eicosene Copolymer, Glycyrrhetinic Acid, Glycyrrhiza Inflata Root Extract, Sodium Hyaluronate, Sodium Ascorbyl Phosphate, Hydroxyacetophenone, Aloe Barbadensis Leaf Juice, 1, 2-Hexanediol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA. 10 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2469,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Water, Urea, Glycerin, Cetearyl Alcohol, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Sodium Lactate, Glyceryl Stearate SE, Distarch Phosphate, Ceramide NP, Lactic Acid, Sodium PCA, Arginine HCl, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil, Sorbitan Stearate, Dimethicone, Phenoxyethanol, Carbomer, Sodium Cetearyl Sulfate, Sodium Chloride</t>
+          <t>Water, Urea, Glycerin, Cetearyl Alcohol, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Ethylhexyl Cocoate, Sodium Lactate, Glyceryl Stearate SE, Distarch Phosphate, Ceramide NP, Lactic Acid, Sodium PCA, Glycine, Alanine, Carnitine, Cholesterol, Sorbitan Stearate, Dimethicone, Phenoxyethanol, Carbomer, Sodium Cetearyl Sulfate, Sodium Chloride</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2462,7 +2488,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Urea, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Hydrogenated Cocoglycerides, Ethylhexyl Cocoate, Sodium Lactate, Distarch Phosphate, Lactic Acid, Sodium PCA, Arginine HCl, Glycine, Alanine, Carnitine, Cholesterol, Helianthus Annuus (Sunflower) Seed Oil</t>
+          <t>unknown — manual review needed: Urea, Caprylic/Capric Triglyceride, Glyceryl Stearate, Octyldodecanol, Ethylhexyl Cocoate, Sodium Lactate, Distarch Phosphate, Lactic Acid, Sodium PCA, Glycine, Alanine, Carnitine, Cholesterol</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2472,12 +2498,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Carbomer); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Roughness Smoothing Body Cream, 16 oz jar. First 3 match brand-site text. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Cream-Fragrance-Free-16-oz-Jar/113158082). Ingredient-name differences: only in the previous text: Hydrogenated Cocoglycerides, Arginine HCl, Helianthus Annuus Seed Oil. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2509,7 +2535,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Water, Urea, Glycerin, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Cetearyl Alcohol, Arginine HCL, Sodium PCA, Lactic Acid, Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Ceramide NP, Alanine, Threonine, Glutamic Acid, Lysine HCL, Sodium Chloride, 1,2-Hexanediol, Phenoxyethanol, Potassium Sorbate.</t>
+          <t>Water, Urea, Glycerin, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Tapioca Starch, Carnitine, Cetearyl Alcohol, Ceramide NP, Arginine HCL, Sodium PCA, Histidine HCl, Lactic Acid, Mannitol, Arginine, Serine, Sucrose, PCA, Citrulline, Glycogen, Alanine, Threonine, Glutamic acid, Lysine HCl, Sodium Chloride, 1,2-Hexanediol, Phenoxyethanol, Potassium Sorbate</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2528,7 +2554,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Urea, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Nylon-12, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Arginine HCL, Sodium PCA, Lactic Acid, Carnitine, Mannitol, Serine, Sucrose, Citrulline, Glycogen, Histidine HCL, Alanine, Threonine, Glutamic Acid, Lysine HCL</t>
+          <t>unknown — manual review needed: Urea, Isopropyl Stearate, Dicaprylyl Ether, Glyceryl Glucoside, Sodium Lactate, Butyrospermum Parkii (Shea) Butter, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Tapioca Starch, Carnitine, Arginine HCL, Sodium PCA, Histidine HCl, Lactic Acid, Mannitol, Arginine, Serine, Sucrose, PCA, Citrulline, Glycogen, Alanine, Threonine, Glutamic acid, Lysine HCl</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2538,12 +2564,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (1,2-Hexanediol, Phenoxyethanol); tier applies to the printed subset only. 22 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (1,2-Hexanediol, Phenoxyethanol); tier applies to the printed subset only. 24 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 22 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Roughness Relief Body Lotion, Fragrance Free, 16.9 fl oz. First 3 match brand-site text. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Roughness-Relief-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/845487111). Ingredient-name differences: only in the full brand list: Tapioca Starch, Arginine, PCA; only in the previous text: Nylon-12. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 24 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2575,7 +2601,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Active Ingredient: 2% colloidal oatmeal - Inactive Ingredients: Water, Isopropyl Palmitate, Glycerin, Cetearyl Alcohol, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Sodium Myreth Sulfate, Cetearyl Isononanoate, Xanthan Gum, Ceramide NP, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Citric Acid, Sodium Chloride, Phenoxyethanol, Carbomer, Sodium Hydroxide, Pentylene Glycol, Decylene Glycol, Sodium Benzoate</t>
+          <t>Active Ingredients: Colloidal Oatmeal (2%) Inactive Ingredients: Isopropyl Palmitate, Glycerin, Cetearyl Alcohol, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Sodium Myreth Sulfate, Cetearyl Isononanoate, Xanthan Gum, Ceramide NP, Alanine, Arginine HCL, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Citric Acid, Sodium Chloride, Phenoxyethanol, Carbomer, Sodium Hydroxide, Pentylene Glycol, Decylene Glycol, Sodium Benzoate</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2594,7 +2620,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCL, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2605,7 +2631,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Identical printed text on 1 other product(s): Baby Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Body Wash, Eczema Relief, 13.5 fl oz. Active 2% colloidal oatmeal matches brand-site text. Walmart prints Active/Inactive labels; kept verbatim. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/274424851). Ingredient-name differences: only in the previous text: Water. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2637,7 +2663,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Active Ingredient: Colloidal Oatmeal 1% Inactive Ingredients: Water, Glycerin, Ricinus Communis (Castor) Seed Oil, Mineral Oil, Cetyl Alcohol, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Cetyl Palmitate, PEG-40 Stearate, Glycyrrhiza Inflata Root Extract, Ceramide NP, 1,2-Hexanediol, Phenoxyethanol, Piroctone Olamine, Caprylyl Glycol, Ethylhexylglycerin, Benzyl Alcohol, Citric Acid.</t>
+          <t>Active Ingredients: Colloidal Oatmeal (1%) Inactive Ingredients: Water, Cetyl Alcohol, Cetyl Palmitate, Ethylhexylglycerin, Phenoxyethanol, Piroctone Olamine, Caprylyl Glycol, Ethylhexylglycerin, Benzyl Alcohol</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2646,17 +2672,17 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylhexylglycerin [4,5]</t>
+          <t>Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2666,12 +2692,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, 1,2-Hexanediol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Ethylhexylglycerin, Phenoxyethanol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Eczema Relief Body Cream, 8 oz, Fragrance Free. Colloidal Oatmeal 1% matches brand-site text. Size not printed on brand listing. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Body-Creme-8-Oz/32239571). Ingredient-name differences: only in the previous text: Glycerin, Ricinus Communis Seed Oil, Mineral Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, PEG-40 Stearate, Glycyrrhiza Inflata Root Extract, Ceramide NP, 1, 2-Hexanediol, Citric Acid. Scrape note: the brand dialog list is much shorter than the earlier captured text (which included Ricinus Communis Seed Oil, Mineral Oil, Glyceryl Stearate, PEG-40 Stearate and others); the brand text is recorded as shown and the grade rests on it. 2 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2703,7 +2729,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Active ingredient: Colloidal Oatmeal 1% ...... Skin Protectant. Inactive Ingredients: Water, Glycerin, Alcohol Denat., Octyldodecanol, Caprylic/Capric Triglyceride, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Ceramide NP, Phytosphingosine, Oleic Acid, Behenyl Alcohol, Cetyl Alcohol, Gellan Gum, Xanthan Gum, Hydroxyacetophenone, Caprylyl Glycol, Citric Acid.</t>
+          <t>Colloidal Oatmeal, Water, Glycerin, Alcohol Denat., Octyldodecanol, Caprylic/Capric Triglyceride, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Ceramide NP, Oleic Acid, Behenyl Alcohol, Cetyl Alcohol, Gellan Gum, Xanthan Gum, Hydroxyacetophenone, Caprylyl Glycol, Citric Acid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2722,18 +2748,18 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Octyldodecanol, Caprylic/Capric Triglyceride, Glycyrrhiza Inflata Root Extract, Phytosphingosine, Gellan Gum, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Octyldodecanol, Caprylic/Capric Triglyceride, Glycyrrhiza Inflata Root Extract, Gellan Gum, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade.</t>
+          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Eczema Relief Hydrogel, Colloidal Oatmeal Skin Protectant, 5 oz tube. Colloidal oatmeal (listed as active, 1%) and the first inactive ingredients Water, Glycerin match brand-site text. Walmart prints the Active section with a 1% strength; brand printed Colloidal Oatmeal, Water, Glycerin. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Hydrogel-Fragrance-Free-Steroid-Free-5-oz-Tube/5382086083). Ingredient-name differences: only in the previous text: Skin Protectant, Phytosphingosine. Identical printed text on 1 other product(s): Eucerin Baby Eczema Relief Hydrogel. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2765,7 +2791,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal 1% Inactive Ingredients: Water, Glycerin, Mineral Oil, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Cetyl Alcohol, Glyceryl Stearate, Cetyl Palmitate, PEG-40 Stearate, Glycyrrhiza Inflata Root Extract, Ceramide NP, Decylene Glycol, 1,2-Hexanediol, Phenoxyethanol, Piroctone Olamine, Caprylyl Glycol, Ethylhexylglycerin, Citric Acid, Menthoxypropanediol, Trisodium EDTA, Benzyl Alcohol, BHT.</t>
+          <t>Active Ingredients: Colloidal Oatmeal (1%) Inactive Ingredients: Water, Glycerin, Mineral Oil, Ricinus Communis Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Cetyl Palmitate, PEG-40 Stearate, Glycyrrhiza Inflata Root Extract, Ceramide NP, Decylene Glycol, 1,2-Hexanediol, Phenoxyethanol, Piroctone Olamine, Caprylyl Glycol, Ethylhexylglycerin, Citric Acid, Menthoxypropanediol, Trisodium EDTA, Benzyl Alcohol, BHT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2784,7 +2810,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Glycyrrhiza Inflata Root Extract, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis Seed Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine, Menthoxypropanediol, Trisodium EDTA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2794,12 +2820,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, Decylene Glycol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, PEG-40 Stearate, Decylene Glycol); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Eczema Relief Flare-Up Treatment Cream, 5 oz tube. Colloidal Oatmeal 1% matches brand-site text. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Eczema-Relief-Flare-Up-Treatment-Cream-5-oz-Tube/374439674). Ingredient-name differences: only in the previous text: Cetyl Alcohol, Glyceryl Stearate. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2865,12 +2891,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
+          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Itch Relief Intensive Calming Body Lotion, 8.4 fl oz. Menthol 0.1% matches brand-site text. Size not printed on brand listing. Audit notes: Retailer fallback 2026-10-17. Brand site shows Active Ingredients only (Menthol 0.1%), no full list. CVS: product pages returned Access Denied (see product 20); not searched for this product. Walgreens: bot-challenge page, not completed. Target: no match. Walmart: 'Eucerin Itch Relief Intensive Calming Body Lotion for Dry, Itchy Skin with Menthol, 8.4 fl oz'; Ingredients block copied verbatim (Active Menthol 0.1% matches the brand). Needs review: the brand page prints no size, and Walmart also lists a 'Eucerin Skin Calming Itch Relief Treatment, 8.4 fl oz' that matches the brand URL slug and was not compared, so product identity is not confirmed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Itch-Relief-Intensive-Calming-Body-Lotion-for-Dry-Itchy-Skin-with-Menthol-8-4-fl-oz/19921454664).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2923,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Cetyl Palmitate, Mineral Oil, Caprylic-Capric-Triglyceride, Octyldodecanol, Cetyl Alcohol, Glyceryl Stearate, Colloidal Oatmeal (Skin Protectant), Dimethicone, Methylpropanediol, PEG-40 Stearate, Phenoxyethanol, 1-2-Hexanediol, Polyglyceryl-2 Caprate, Piroctone Olamine, Benzyl Alcohol, Carbomer, Decylene Glycol</t>
+          <t>Water, Glycerin, Cetyl Palmitate, Octyldodecanol, Cetyl Alcohol, Colloidal Oatmeal, Dimethicone, Phenoxyethanol, 1,2-Hexanediol, Piroctone Olamine, Benzyl Alcohol, Carbomer, Carbomer</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2906,17 +2932,17 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Dimethicone [2,6] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / Phenoxyethanol [1,2,4,5,8] / 1-2-Hexanediol [1,2] / Carbomer [1,4,6] / Decylene Glycol [1,2] (inferred: -glycol)</t>
+          <t>Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8] / 1,2-Hexanediol [1,2] / Carbomer [1,4,6]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: caprylic/capric triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Octyldodecanol, Colloidal Oatmeal, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2926,12 +2952,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, 1,2-Hexanediol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Skin Calming Body Lotion, 16.9 fl oz. First 3 match brand-site text. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Body-Lotion-For-Dry-Itchy-Skin-16-9-Fl-Oz-Bottle/45809149). Ingredient-name differences: only in the full brand list: 1, 2-Hexanediol; only in the previous text: Mineral Oil, Caprylic-Capric-Triglyceride, Glyceryl Stearate, Methylpropanediol, PEG-40 Stearate, 1-2-Hexanediol, Polyglyceryl-2 Caprate, Decylene Glycol. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 3 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2963,7 +2989,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Cetyl Palmitate, Mineral Oil, Caprylic/Capric Triglyceride, Octyldodecanol, Cetyl Alcohol, Glyceryl Stearate, Colloidal Oatmeal, Dimethicone, Methylpropanediol, PEG-40 Stearate, 1,2-Hexanediol, Phenoxyethanol, Piroctone Olamine, Carbomer, Benzyl Alcohol, Polyglyceryl-2 Caprate, Decylene Glycol</t>
+          <t>Water, Glycerin, Cetyl Palmitate, Octyldodecanol, Cetyl Alcohol, Colloidal Oatmeal, Dimethicone, Methylpropanediol, 1,2-Hexanediol, Phenoxyethanol, Benzyl Alcohol, Polyglyceryl-2 Caprate, Polyglyceryl-2 Caprate, Decylene Glycol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2972,17 +2998,17 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Dimethicone [2,6] / PEG-40 Stearate [1,2,4,5] (inferred: PEG-) / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Decylene Glycol [1,2] (inferred: -glycol)</t>
+          <t>Dimethicone [2,6] / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Decylene Glycol [1,2] (inferred: -glycol)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Octyldodecanol, Glyceryl Stearate, Colloidal Oatmeal, Methylpropanediol, Piroctone Olamine, Polyglyceryl-2 Caprate</t>
+          <t>unknown — manual review needed: Octyldodecanol, Colloidal Oatmeal, Methylpropanediol, Polyglyceryl-2 Caprate</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2992,12 +3018,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, PEG-40 Stearate); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Dimethicone, 1,2-Hexanediol, Phenoxyethanol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Skin Calming Body Cream, Fragrance Free, 8 oz. First 3 match brand-site text. Size not printed on brand listing. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Skin-Calming-Daily-Moisturizing-Cream-for-Dry-Itchy-Skin-8-oz-Tube/11997299). Ingredient-name differences: only in the previous text: Mineral Oil, Caprylic/Capric Triglyceride, Glyceryl Stearate, PEG-40 Stearate, Piroctone Olamine, Carbomer. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3029,38 +3055,47 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Octisalate (3.5)</t>
+          <t>Active Ingredients: Octisalate (3.5)
+Inactive Ingredients: Glycerin, Methylpropanediol, Titanium Dioxide, Butyrospermum Parkii (Shea) Butter, Cetearyl Alcohol, Pentylene Glycol, Dimethicone, Glycyrrhiza Inflata Root Extract, Potassium Cetyl Phosphate, Caprylyl Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Xanthan Gum, Phenoxyethanol, Chromium Oxide Greens, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Octisalate [2]</t>
+          <t>Octisalate [2] / Pentylene Glycol [1,2] / Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Methylpropanediol, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Inflata Root Extract, Potassium Cetyl Phosphate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Chromium Oxide Greens, Sodium Hydroxide</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Ungradable: source text unresolved (practitioner exception, 2026-10-17). Partial flags recorded: 1.</t>
+          <t>4 flagged ingredient(s) in the printed list (Octisalate, Pentylene Glycol, Dimethicone); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CVS Eucerin Daily Hydration Broad Spectrum SPF 15 Body Lotion, 16.9 OZ (prodid 1013203) is not a clear match and not used. Its printed actives are Avobenzone 2.0%, Homosalate 3.4%, Octisalate 3.4%, Octocrylene 4.7%, while the brand key is Octisalate (3.5). The brand row is the Daily Protection SPF 15 moisturizer, a different product name. Walmart 912642578 and Amazon B082D8S4W3 / B00KIHJO3E print no ingredient text (round 1). Dermstore and Walgreens not usable. Unresolved. Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2: CVS Eucerin Daily Hydration Broad Spectrum SPF 15 Body Lotion, 16.9 OZ (prodid 1013203) is not a clear match and not used. Its printed actives are Avobenzone 2.0%, Homosalate 3.4%, Octisalate 3.4%, Octocrylene 4.7%, while the brand key is Octisalate (3.5). The brand row is the Daily Protection SPF 15 moisturizer, a different product name. Walmart 912642578 and Amazon B082D8S4W3 / B00KIHJO3E print no ingredient text (round 1). Dermstore and Walgreens not usable. Unresolved. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: none recorded (key ingredients only). Ingredient-name differences: only in the full brand list: Glycerin, Methylpropanediol, Titanium Dioxide, Butyrospermum Parkii Butter, Cetearyl Alcohol, Pentylene Glycol, Dimethicone, Glycyrrhiza Inflata Root Extract, Potassium Cetyl Phosphate, Caprylyl Glycol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Xanthan Gum, Phenoxyethanol, Chromium Oxide Greens, Sodium Hydroxide. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3087,38 +3122,47 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sunflower Seed oil</t>
+          <t>Active Ingredients: Sunflower Seed oil
+Inactive Ingredients: Helianthus Annuus (Sunflower) Seed Oil, Petrolatum, Glycerin, Glyceryl Stearate SE, Octyldodecanol, Caprylic/Capric Triglyceride, Pentylene Glycol, Palmitic Acid, Stearic Acid, Phenoxyethanol, Dimethicone, Cetearyl Alcohol, Caprylyl Glycol, Panthenol, Tocopheryl Acetate, Cholesterol, Carbomer, Sodium Hydroxide, Trisodium EDTA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Petrolatum [1] / Pentylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Dimethicone [2,6] / Carbomer [1,4,6]</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: helianthus annuus (sunflower) seed oil</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>unknown — manual review needed: helianthus annuus (sunflower) seed oil, Octyldodecanol, Caprylic/Capric Triglyceride, Palmitic Acid, Stearic Acid, Tocopheryl Acetate, Cholesterol, Sodium Hydroxide, Trisodium EDTA</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Ungradable: source text unresolved (practitioner exception, 2026-10-17). Partial flags recorded: 0.</t>
+          <t>5 flagged ingredient(s) in the printed list (Petrolatum, Pentylene Glycol, Phenoxyethanol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. 1 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 1 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: helianthus annuus (sunflower) seed oil.</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Daily Hydration Body Lotion, 16.9 OZ (prodid 1013215) prints a full list with sunflower seed oil as the first active. The brand prints only the single key ingredient (Sunflower Seed oil) and no size, so the cross-check cannot be done and the variant is not clearly the brand product. Amazon multipack (3 x 16.9 fl oz) is also a candidate only. Unresolved. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: none recorded (key ingredients only). Ingredient-name differences: only in the full brand list: Helianthus Annuus Seed Oil, Petrolatum, Glycerin, Glyceryl Stearate SE, Octyldodecanol, Caprylic/Capric Triglyceride, Pentylene Glycol, Palmitic Acid, Stearic Acid, Phenoxyethanol, Dimethicone, Cetearyl Alcohol, Caprylyl Glycol, Panthenol, Tocopheryl Acetate, Cholesterol, Carbomer, Sodium Hydroxide, Trisodium EDTA. Candidate retailer listing removed (CVS 16.9 OZ); its text differs from the brand list (similarity 0.88), so it is not a match. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3223,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. 3 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Original Healing Body Cream, 16 oz jar. First 3 match brand-site text. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Cream-for-Extra-Dry-Compromised-Skin-16-oz-Jar/1120749). Previous verbatim text was identical to the full list. 3 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3211,7 +3255,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Water, Mineral Oil, Isopropyl Palmitate, Sorbitol, Propylene Glycol, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Cetyl Palmitate, Magnesium Sulfate, Aluminum Stearates, Phenoxyethanol, Lanolin Alcohol, Sodium Citrate, Citric Acid, Potassium Sorbate.</t>
+          <t>Mineral Oil, Isopropyl Palmitate, Sorbitol, Propylene Glycol, Diisostearoyl Polyglyceryl-3 Dimer Dilinoleate, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Cetyl Palmitate, Magnesium Sulfate, Aluminum Stearates, Phenoxyethanol, Lanolin Alcohol, Sodium Citrate, Citric Acid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3245,7 +3289,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Original Healing Body Lotion, Fragrance Free, 16.9 fl oz. Brand-site key list (Mineral Oil, Isopropyl Palmitate, Sorbitol) appears in the same order in this list, after Water. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Original-Healing-Body-Lotion-Fragrance-Free-16-9-fl-oz-Bottle/11997298). Ingredient-name differences: only in the previous text: Water, Potassium Sorbate. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3277,38 +3321,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Colloidal Oatmeal, Water, Glycerin</t>
+          <t>Colloidal Oatmeal, Water, Glycerin, Alcohol Denat., Octyldodecanol, Caprylic/Capric Triglyceride, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Ceramide NP, Oleic Acid, Behenyl Alcohol, Cetyl Alcohol, Gellan Gum, Xanthan Gum, Hydroxyacetophenone, Caprylyl Glycol, Citric Acid</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Alcohol Denat [4] (inferred: alcohol denat)</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Octyldodecanol, Caprylic/Capric Triglyceride, Glycyrrhiza Inflata Root Extract, Gellan Gum, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Ungradable: source text unresolved (practitioner exception, 2026-10-17). Partial flags recorded: 0.</t>
+          <t>1 flagged ingredient(s) in the printed list (Alcohol Denat); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 1 unknown ingredient(s) excluded from flags (2026-10-17). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Colloidal Oatmeal.</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2: CONFLICT, not used. Amazon Eucerin Baby Eczema Relief Hydrogel 5 FL OZ (ASIN B0DFJQVMD7, sold by Amazon.com) prints an Ingredients block that starts Water, Glycerin, Alcohol Denat. and does not list Colloidal Oatmeal, the first brand key ingredient. The Walmart copy also has no Colloidal Oatmeal. Brand text conflicts with both retailers; held at needs review with both kept. CVS: no baby hydrogel found (only the adult Eucerin Eczema Relief Hydrogel Moisturizer, not used). Dermstore search returned no results. Walgreens blocked; Ulta holding page. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: none recorded (key ingredients only). Ingredient-name differences: only in the full brand list: Alcohol Denat, Octyldodecanol, Caprylic/Capric Triglyceride, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Ceramide NP, Oleic Acid, Behenyl Alcohol, Cetyl Alcohol, Gellan Gum, Xanthan Gum, Hydroxyacetophenone, Caprylyl Glycol, Citric Acid. Candidate retailer listing removed (Amazon 5 FL OZ); its text differs from the brand list (similarity 0.93), so it is not a match. Identical printed text on 1 other product(s): Eucerin Eczema Relief Hydrogel. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3383,8 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Active Ingredient: 2% colloidal oatmeal - Inactive Ingredients: Water, Isopropyl Palmitate, Glycerin, Cetearyl Alcohol, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Sodium Myreth Sulfate, Cetearyl Isononanoate, Xanthan Gum, Ceramide NP, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Citric Acid, Sodium Chloride, Phenoxyethanol, Carbomer, Sodium Hydroxide, Pentylene Glycol, Decylene Glycol, Sodium Benzoate</t>
+          <t>Active Ingredients: Colloidal Oatmeal (2%)
+Inactive Ingredients: Water, Isopropyl Palmitate, Glycerin, Cetearyl Alcohol, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Sodium Myreth Sulfate, Cetearyl Isononanoate, Xanthan Gum, Ceramide NP, Alanine, Arginine HCL, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Citric Acid, Sodium Chloride, Phenoxyethanol, Carbomer, Sodium Hydroxide, Pentylene Glycol, Decylene Glycol, Sodium Benzoate</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3354,7 +3403,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: colloidal oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCl, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Isopropyl Palmitate, Sodium Cocoamphoacetate, Caprylic/Capric Triglyceride, Octyldodecanol, C12-15 Alkyl Benzoate, Cetearyl Isononanoate, Alanine, Arginine HCL, Carnitine, Glycine, Sodium PCA, Lauryl Glucoside, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3365,7 +3414,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Identical printed text on 1 other product(s): Eczema Relief Cream &amp; Body Wash. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Cream Body Wash, 13.5 fl oz. 2% colloidal oatmeal matches brand-site text. Walmart text is identical to the adult Eczema Relief Cream Body Wash listing (274424851); the duplicate is noted, not treated as a conflict. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Cream-Body-Wash-Fragrance-Free-13-5-fl-oz-Bottle/716276271). Same ingredient names as the previous text; wording, spelling or order differs. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3397,7 +3446,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Water, Decyl Glucoside, Sodium Myreth Sulfate</t>
+          <t>Water, Decyl Glucoside, Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine, Sodium Chloride, Panthenol, Butyrospermum Parkii (Shea) Butter, Polyquaternium-10, Citric Acid, Sodium Benzoate</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3406,29 +3455,33 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate)</t>
+          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / PEG-200 Hydrogenated Glyceryl Palmate [1,2,4,5] (inferred: PEG-) / Cocamidopropyl Betaine [1,4] / Polyquaternium-10 [2] (inferred: -nium quat)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate); tier applies to the printed subset only.</t>
+          <t>4 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: No usable text. CVS brand shop and search returned no Eucerin Baby Wash and Shampoo. Amazon search returned only a third-party Awiaub pack of three (13.5 oz), not a clear match, not used. Walmart 682440208 and 14819669289 print no ingredient text (round 1). Walgreens blocked; Ulta holding page. Unresolved. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2: No usable text. CVS brand shop and search returned no Eucerin Baby Wash and Shampoo. Amazon search returned only a third-party Awiaub pack of three (13.5 oz), not a clear match, not used. Walmart 682440208 and 14819669289 print no ingredient text (round 1). Walgreens blocked; Ulta holding page. Unresolved. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: none recorded (key ingredients only). Ingredient-name differences: only in the full brand list: PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine, Sodium Chloride, Panthenol, Butyrospermum Parkii Butter, Polyquaternium-10, Citric Acid, Sodium Benzoate. Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). 1 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3508,8 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Active Ingredient: Colloidal Oatmeal 1% (Skin protectant). Inactive Ingredients: Water, Glycerin, Ricinus Communis (Castor) Seed Oil, Mineral Oil, Cetyl Alcohol, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Cetyl Palmitate, PEG-40 Stearate, Glycyrrhiza Inflata Root Extract, Ceramide NP, 1,2-Hexanediol, Phenoxyethanol, Piroctone Olamine, Caprylyl Glycol, Ethylhexylglycerin, Benzyl Alcohol, Citric Acid.</t>
+          <t>Active Ingredients: Colloidal Oatmeal (1%)
+Inactive Ingredients: Water, Glycerin, Ricinus Communis Seed Oil, Mineral Oil, Cetyl Alcohol, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Cetyl Palmitate, PEG-40 Stearate, Glycyrrhiza Inflata Root Extract, Ceramide NP, 1,2-Hexanediol, Phenoxyethanol, Piroctone Olamine, Caprylyl Glycol, Ethylhexylglycerin, Benzyl Alcohol, Citric Acid</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3474,7 +3528,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis (Castor) Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine</t>
+          <t>unknown — manual review needed: Colloidal Oatmeal, Ricinus Communis Seed Oil, Glyceryl Stearate, Caprylic/Capric Triglyceride, Octyldodecanol, Glycyrrhiza Inflata Root Extract, Piroctone Olamine</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3489,7 +3543,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients/Active Ingredients block (no key-ingredients disclaimer). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin Baby Eczema Relief Body Cream, 5 oz. Colloidal Oatmeal 1% matches brand-site text. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/Eucerin-Baby-Eczema-Relief-Body-Cream-5-0-oz/35930944). Same ingredient names as the previous text; wording, spelling or order differs. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3521,38 +3575,46 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dexpanthenol</t>
+          <t>Water, Cetyl Palmitate, Glycerin, Mineral Oil, Cetyl Alcohol, Polybutene, Sorbitan Stearate, Tapioca Starch, Panthenol, Butyrospermum Parkii (Shea) Butter, Dimethicone, Phenoxyethanol, Carbomer, Pentylene Glycol, Caprylyl Glycol, Sodium Hydroxide, Sodium Citrate, Citric Acid</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Mineral Oil [1] / Dimethicone [2,6] / Phenoxyethanol [1,2,4,5,8] / Carbomer [1,4,6] / Pentylene Glycol [1,2]</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Dexpanthenol</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>unknown — manual review needed: Polybutene, Tapioca Starch, Butyrospermum Parkii (Shea) Butter, Sodium Hydroxide</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Ungradable: source text unresolved (practitioner exception, 2026-10-17). Partial flags recorded: 0.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, Dimethicone, Phenoxyethanol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Printed block: Ingredients (key-ingredients disclaimer shown). Site limitation: No product page publishes a full INCI list. Each Ingredients block prints only key ingredients (its own disclaimer says 'Learn more about the key ingredients of this product'); sunscreen and oatmeal products print 'Active Ingredients' with percentages only. Grades in this audit are on the printed subset only. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. 1 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 1 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule). Moved to ungradable: source text unresolved (practitioner exception, 2026-10-17, change 3). Unknown kept: Dexpanthenol.</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Round 2: candidate only, not used. CVS Eucerin Baby Body Lotion, 13.5 OZ (prodid 1030497) prints a full list with Panthenol as the active (the INCI name for the brand key Dexpanthenol). The brand prints one key ingredient and no size, so the cross-check cannot be done. Walmart 13.5 fl oz Baby Lotion (Panthenol, fragrance free) is also a candidate only. Unresolved. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: none recorded (key ingredients only). Ingredient-name differences: only in the full brand list: Water, Cetyl Palmitate, Glycerin, Mineral Oil, Cetyl Alcohol, Polybutene, Sorbitan Stearate, Tapioca Starch, Panthenol, Butyrospermum Parkii Butter, Dimethicone, Phenoxyethanol, Carbomer, Pentylene Glycol, Caprylyl Glycol, Sodium Hydroxide, Sodium Citrate, Citric Acid; only in the previous text: Dexpanthenol. Candidate retailer listing removed (CVS 13.5 OZ); its text differs from the brand list (similarity 0.93), so it is not a match. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>

--- a/audits/eucerin/eucerin_audit.xlsx
+++ b/audits/eucerin/eucerin_audit.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Water, Alcohol Denat., Butylene Glycol, Glycerin, Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Cetearyl Alcohol, Distarch Phosphate, Sodium Ascorbyl Phosphate, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Tocopherol, Glucosylrutin, Sodium Stearoyl Glutamate, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Xanthan Gum, Gellan Gum, Dimethicone, Isoquercitrin, Citric Acid, Sodium Chloride, Ethylhexylglycerin, Trisodium EDTA, Phenoxyethanol</t>
+          <t>Water, Alcohol Denat., Butylene Glycol, Glycerin, Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Cetearyl Alcohol, Distarch Phosphate, Sodium Ascorbyl Phosphate, Sodium Hyaluronate, Glycyrrhiza Inflata Root Extract, Tocopherol, Glucosylrutin, Sodium Stearoyl Glutamate, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Xanthan Gum, Gellan Gum, Dimethicone, Isoquercitrin, Citric Acid, Sodium Chloride, Ethylhexylglycerin, Trisodium EDTA, Phenoxyethanol, Isobutylamido Thiazolyl Resorcinol, Glycine Soja Oil, Fragrance</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -912,17 +912,17 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat) / Butylene Glycol [1,2] / Dimethicone [2,6] / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Butylene Glycol [1,2] / Dimethicone [2,6] / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8] / Fragrance [1,2,4,8] (fragrance without disclosure)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Sodium Stearoyl Glutamate, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Gellan Gum, Isoquercitrin, Trisodium EDTA</t>
+          <t>unknown — manual review needed: Isopropyl Palmitate, Cetearyl Isononanoate, Diisopropyl Adipate, Propylheptyl Caprylate, Distarch Phosphate, Sodium Ascorbyl Phosphate, Glycyrrhiza Inflata Root Extract, Glucosylrutin, Sodium Stearoyl Glutamate, Glyceryl Stearate, Hydroxypropyl Starch Phosphate, Dehydroxanthan Gum, Gellan Gum, Isoquercitrin, Trisodium EDTA, Isobutylamido Thiazolyl Resorcinol, Glycine Soja Oil</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, Dimethicone); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Butylene Glycol, Dimethicone); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648). Ingredient-name differences: only in the previous text: Isobutylamido Thiazolyl Resorcinol, Glycine Soja Oil, Fragrance. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
+          <t>Printed block: full expanded list. Site limitation: Brand site (2026-10-17 merge): 44 of 48 products show a full ingredient list after Learn more &gt; View all. Products 20, 21, 22 and 36 print only Active Ingredients on the brand site (no inactive list); see the retailer fallback notes for those four. Retailer notes: Walmart listing Eucerin, Radiant Tone Dual Serum, 1 fl oz. First 3 match brand-site text. Fragrance listed without breakdown. Audit notes: Verbatim replaced 2026-10-17 with the full brand-site list (Learn more, View all). Previous verbatim source: Walmart (https://www.walmart.com/ip/EES-RDNT-TN-DUAL-SERUM-1-FLOZ/13164009648). Ingredient-name differences: only in the previous text: Isobutylamido Thiazolyl Resorcinol, Glycine Soja Oil, Fragrance. 2026-10-17 practitioner decision: Isobutylamido Thiazolyl Resorcinol (Thiamidol), Glycine Soja Oil and Fragrance added from the earlier Walmart listing, because the brand-site list omits them. Appended at the end; the position in the printed list is not verified. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Eucerin brand site, full list (Learn more, View all).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
